--- a/projetos/gestao-ia-planilhas/produto/kit-completo/04-projetos-e-prazos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/04-projetos-e-prazos.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
-        <f>IFERROR(AVERAGEIFS(Etapas!$F$5:$F$304,Etapas!$B$5:$B$304,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(Etapas!$L$5:$L$304,Etapas!$B$5:$B$304,"&lt;&gt;"),0)</f>
         <v>0.545</v>
       </c>
       <c r="H5" s="14" t="n"/>
@@ -1067,7 +1067,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="24">
-        <f>IF(OR(Config!$A$10="",D9=0),"",AVERAGEIFS(Etapas!$F$5:$F$304,Etapas!$A$5:$A$304,Config!$A$10))</f>
+        <f>IF(OR(Config!$A$10="",D9=0),"",AVERAGEIFS(Etapas!$L$5:$L$304,Etapas!$A$5:$A$304,Config!$A$10))</f>
         <v>0.614285714285714</v>
       </c>
       <c r="H9" s="22" t="str">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="24">
-        <f>IF(OR(Config!$A$11="",D10=0),"",AVERAGEIFS(Etapas!$F$5:$F$304,Etapas!$A$5:$A$304,Config!$A$11))</f>
+        <f>IF(OR(Config!$A$11="",D10=0),"",AVERAGEIFS(Etapas!$L$5:$L$304,Etapas!$A$5:$A$304,Config!$A$11))</f>
         <v>0.3</v>
       </c>
       <c r="H10" s="22" t="str">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="24">
-        <f>IF(OR(Config!$A$12="",D11=0),"",AVERAGEIFS(Etapas!$F$5:$F$304,Etapas!$A$5:$A$304,Config!$A$12))</f>
+        <f>IF(OR(Config!$A$12="",D11=0),"",AVERAGEIFS(Etapas!$L$5:$L$304,Etapas!$A$5:$A$304,Config!$A$12))</f>
         <v>0.325</v>
       </c>
       <c r="H11" s="22" t="str">
@@ -1169,7 +1169,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="24">
-        <f>IF(OR(Config!$A$13="",D12=0),"",AVERAGEIFS(Etapas!$F$5:$F$304,Etapas!$A$5:$A$304,Config!$A$13))</f>
+        <f>IF(OR(Config!$A$13="",D12=0),"",AVERAGEIFS(Etapas!$L$5:$L$304,Etapas!$A$5:$A$304,Config!$A$13))</f>
         <v>0.95</v>
       </c>
       <c r="H12" s="22" t="str">
@@ -1203,7 +1203,7 @@
         <v/>
       </c>
       <c r="G13" s="24">
-        <f>IF(OR(Config!$A$14="",D13=0),"",AVERAGEIFS(Etapas!$F$5:$F$304,Etapas!$A$5:$A$304,Config!$A$14))</f>
+        <f>IF(OR(Config!$A$14="",D13=0),"",AVERAGEIFS(Etapas!$L$5:$L$304,Etapas!$A$5:$A$304,Config!$A$14))</f>
         <v/>
       </c>
       <c r="H13" s="22">
@@ -1237,7 +1237,7 @@
         <v/>
       </c>
       <c r="G14" s="24">
-        <f>IF(OR(Config!$A$15="",D14=0),"",AVERAGEIFS(Etapas!$F$5:$F$304,Etapas!$A$5:$A$304,Config!$A$15))</f>
+        <f>IF(OR(Config!$A$15="",D14=0),"",AVERAGEIFS(Etapas!$L$5:$L$304,Etapas!$A$5:$A$304,Config!$A$15))</f>
         <v/>
       </c>
       <c r="H14" s="22">
@@ -1271,7 +1271,7 @@
         <v/>
       </c>
       <c r="G15" s="24">
-        <f>IF(OR(Config!$A$16="",D15=0),"",AVERAGEIFS(Etapas!$F$5:$F$304,Etapas!$A$5:$A$304,Config!$A$16))</f>
+        <f>IF(OR(Config!$A$16="",D15=0),"",AVERAGEIFS(Etapas!$L$5:$L$304,Etapas!$A$5:$A$304,Config!$A$16))</f>
         <v/>
       </c>
       <c r="H15" s="22">
@@ -1305,7 +1305,7 @@
         <v/>
       </c>
       <c r="G16" s="24">
-        <f>IF(OR(Config!$A$17="",D16=0),"",AVERAGEIFS(Etapas!$F$5:$F$304,Etapas!$A$5:$A$304,Config!$A$17))</f>
+        <f>IF(OR(Config!$A$17="",D16=0),"",AVERAGEIFS(Etapas!$L$5:$L$304,Etapas!$A$5:$A$304,Config!$A$17))</f>
         <v/>
       </c>
       <c r="H16" s="22">
@@ -1339,7 +1339,7 @@
         <v/>
       </c>
       <c r="G17" s="24">
-        <f>IF(OR(Config!$A$18="",D17=0),"",AVERAGEIFS(Etapas!$F$5:$F$304,Etapas!$A$5:$A$304,Config!$A$18))</f>
+        <f>IF(OR(Config!$A$18="",D17=0),"",AVERAGEIFS(Etapas!$L$5:$L$304,Etapas!$A$5:$A$304,Config!$A$18))</f>
         <v/>
       </c>
       <c r="H17" s="22">
@@ -1373,7 +1373,7 @@
         <v/>
       </c>
       <c r="G18" s="24">
-        <f>IF(OR(Config!$A$19="",D18=0),"",AVERAGEIFS(Etapas!$F$5:$F$304,Etapas!$A$5:$A$304,Config!$A$19))</f>
+        <f>IF(OR(Config!$A$19="",D18=0),"",AVERAGEIFS(Etapas!$L$5:$L$304,Etapas!$A$5:$A$304,Config!$A$19))</f>
         <v/>
       </c>
       <c r="H18" s="22">
@@ -5600,7 +5600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K304"/>
+  <dimension ref="A1:L304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5614,6 +5614,7 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="6" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5728,6 +5729,10 @@
         <f>IF(OR(B5="",G5="Concluída"),0,IF(G5="Atrasada",3000+MIN(Config!$B$5-E5,60),IF(G5="Vence em breve",2000-(E5-Config!$B$5),IF(G5="Em andamento",1000-MIN(E5-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L5" s="35">
+        <f>IF(B5="","",IF(I5&lt;&gt;"",1,N(F5)))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="32" t="inlineStr">
@@ -5770,6 +5775,10 @@
         <f>IF(OR(B6="",G6="Concluída"),0,IF(G6="Atrasada",3000+MIN(Config!$B$5-E6,60),IF(G6="Vence em breve",2000-(E6-Config!$B$5),IF(G6="Em andamento",1000-MIN(E6-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L6" s="35">
+        <f>IF(B6="","",IF(I6&lt;&gt;"",1,N(F6)))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="32" t="inlineStr">
@@ -5811,6 +5820,10 @@
       <c r="K7" s="35">
         <f>IF(OR(B7="",G7="Concluída"),0,IF(G7="Atrasada",3000+MIN(Config!$B$5-E7,60),IF(G7="Vence em breve",2000-(E7-Config!$B$5),IF(G7="Em andamento",1000-MIN(E7-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
+      </c>
+      <c r="L7" s="35">
+        <f>IF(B7="","",IF(I7&lt;&gt;"",1,N(F7)))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -5852,6 +5865,10 @@
         <f>IF(OR(B8="",G8="Concluída"),0,IF(G8="Atrasada",3000+MIN(Config!$B$5-E8,60),IF(G8="Vence em breve",2000-(E8-Config!$B$5),IF(G8="Em andamento",1000-MIN(E8-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>1997.99992</v>
       </c>
+      <c r="L8" s="35">
+        <f>IF(B8="","",IF(I8&lt;&gt;"",1,N(F8)))</f>
+        <v>0.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="32" t="inlineStr">
@@ -5892,6 +5909,10 @@
         <f>IF(OR(B9="",G9="Concluída"),0,IF(G9="Atrasada",3000+MIN(Config!$B$5-E9,60),IF(G9="Vence em breve",2000-(E9-Config!$B$5),IF(G9="Em andamento",1000-MIN(E9-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>3004.99991</v>
       </c>
+      <c r="L9" s="35">
+        <f>IF(B9="","",IF(I9&lt;&gt;"",1,N(F9)))</f>
+        <v>0.7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="32" t="inlineStr">
@@ -5932,6 +5953,10 @@
         <f>IF(OR(B10="",G10="Concluída"),0,IF(G10="Atrasada",3000+MIN(Config!$B$5-E10,60),IF(G10="Vence em breve",2000-(E10-Config!$B$5),IF(G10="Em andamento",1000-MIN(E10-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>99.9999</v>
       </c>
+      <c r="L10" s="35">
+        <f>IF(B10="","",IF(I10&lt;&gt;"",1,N(F10)))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="32" t="inlineStr">
@@ -5972,6 +5997,10 @@
         <f>IF(OR(B11="",G11="Concluída"),0,IF(G11="Atrasada",3000+MIN(Config!$B$5-E11,60),IF(G11="Vence em breve",2000-(E11-Config!$B$5),IF(G11="Em andamento",1000-MIN(E11-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>99.99989</v>
       </c>
+      <c r="L11" s="35">
+        <f>IF(B11="","",IF(I11&lt;&gt;"",1,N(F11)))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="32" t="inlineStr">
@@ -6013,6 +6042,10 @@
       <c r="K12" s="35">
         <f>IF(OR(B12="",G12="Concluída"),0,IF(G12="Atrasada",3000+MIN(Config!$B$5-E12,60),IF(G12="Vence em breve",2000-(E12-Config!$B$5),IF(G12="Em andamento",1000-MIN(E12-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
+      </c>
+      <c r="L12" s="35">
+        <f>IF(B12="","",IF(I12&lt;&gt;"",1,N(F12)))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -6054,6 +6087,10 @@
         <f>IF(OR(B13="",G13="Concluída"),0,IF(G13="Atrasada",3000+MIN(Config!$B$5-E13,60),IF(G13="Vence em breve",2000-(E13-Config!$B$5),IF(G13="Em andamento",1000-MIN(E13-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>1999.99987</v>
       </c>
+      <c r="L13" s="35">
+        <f>IF(B13="","",IF(I13&lt;&gt;"",1,N(F13)))</f>
+        <v>0.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="32" t="inlineStr">
@@ -6094,6 +6131,10 @@
         <f>IF(OR(B14="",G14="Concluída"),0,IF(G14="Atrasada",3000+MIN(Config!$B$5-E14,60),IF(G14="Vence em breve",2000-(E14-Config!$B$5),IF(G14="Em andamento",1000-MIN(E14-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>99.99986</v>
       </c>
+      <c r="L14" s="35">
+        <f>IF(B14="","",IF(I14&lt;&gt;"",1,N(F14)))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="32" t="inlineStr">
@@ -6134,6 +6175,10 @@
         <f>IF(OR(B15="",G15="Concluída"),0,IF(G15="Atrasada",3000+MIN(Config!$B$5-E15,60),IF(G15="Vence em breve",2000-(E15-Config!$B$5),IF(G15="Em andamento",1000-MIN(E15-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>99.99985</v>
       </c>
+      <c r="L15" s="35">
+        <f>IF(B15="","",IF(I15&lt;&gt;"",1,N(F15)))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="32" t="inlineStr">
@@ -6174,6 +6219,10 @@
         <f>IF(OR(B16="",G16="Concluída"),0,IF(G16="Atrasada",3000+MIN(Config!$B$5-E16,60),IF(G16="Vence em breve",2000-(E16-Config!$B$5),IF(G16="Em andamento",1000-MIN(E16-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>99.99984</v>
       </c>
+      <c r="L16" s="35">
+        <f>IF(B16="","",IF(I16&lt;&gt;"",1,N(F16)))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="32" t="inlineStr">
@@ -6215,6 +6264,10 @@
       <c r="K17" s="35">
         <f>IF(OR(B17="",G17="Concluída"),0,IF(G17="Atrasada",3000+MIN(Config!$B$5-E17,60),IF(G17="Vence em breve",2000-(E17-Config!$B$5),IF(G17="Em andamento",1000-MIN(E17-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
+      </c>
+      <c r="L17" s="35">
+        <f>IF(B17="","",IF(I17&lt;&gt;"",1,N(F17)))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -6256,6 +6309,10 @@
         <f>IF(OR(B18="",G18="Concluída"),0,IF(G18="Atrasada",3000+MIN(Config!$B$5-E18,60),IF(G18="Vence em breve",2000-(E18-Config!$B$5),IF(G18="Em andamento",1000-MIN(E18-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>1997.99982</v>
       </c>
+      <c r="L18" s="35">
+        <f>IF(B18="","",IF(I18&lt;&gt;"",1,N(F18)))</f>
+        <v>0.3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="32" t="inlineStr">
@@ -6296,6 +6353,10 @@
         <f>IF(OR(B19="",G19="Concluída"),0,IF(G19="Atrasada",3000+MIN(Config!$B$5-E19,60),IF(G19="Vence em breve",2000-(E19-Config!$B$5),IF(G19="Em andamento",1000-MIN(E19-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>99.99981</v>
       </c>
+      <c r="L19" s="35">
+        <f>IF(B19="","",IF(I19&lt;&gt;"",1,N(F19)))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="32" t="inlineStr">
@@ -6336,6 +6397,10 @@
         <f>IF(OR(B20="",G20="Concluída"),0,IF(G20="Atrasada",3000+MIN(Config!$B$5-E20,60),IF(G20="Vence em breve",2000-(E20-Config!$B$5),IF(G20="Em andamento",1000-MIN(E20-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>99.9998</v>
       </c>
+      <c r="L20" s="35">
+        <f>IF(B20="","",IF(I20&lt;&gt;"",1,N(F20)))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="32" t="inlineStr">
@@ -6378,6 +6443,10 @@
         <f>IF(OR(B21="",G21="Concluída"),0,IF(G21="Atrasada",3000+MIN(Config!$B$5-E21,60),IF(G21="Vence em breve",2000-(E21-Config!$B$5),IF(G21="Em andamento",1000-MIN(E21-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L21" s="35">
+        <f>IF(B21="","",IF(I21&lt;&gt;"",1,N(F21)))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="32" t="inlineStr">
@@ -6420,6 +6489,10 @@
         <f>IF(OR(B22="",G22="Concluída"),0,IF(G22="Atrasada",3000+MIN(Config!$B$5-E22,60),IF(G22="Vence em breve",2000-(E22-Config!$B$5),IF(G22="Em andamento",1000-MIN(E22-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L22" s="35">
+        <f>IF(B22="","",IF(I22&lt;&gt;"",1,N(F22)))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="32" t="inlineStr">
@@ -6461,6 +6534,10 @@
       <c r="K23" s="35">
         <f>IF(OR(B23="",G23="Concluída"),0,IF(G23="Atrasada",3000+MIN(Config!$B$5-E23,60),IF(G23="Vence em breve",2000-(E23-Config!$B$5),IF(G23="Em andamento",1000-MIN(E23-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
+      </c>
+      <c r="L23" s="35">
+        <f>IF(B23="","",IF(I23&lt;&gt;"",1,N(F23)))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -6501,6 +6578,10 @@
       <c r="K24" s="35">
         <f>IF(OR(B24="",G24="Concluída"),0,IF(G24="Atrasada",3000+MIN(Config!$B$5-E24,60),IF(G24="Vence em breve",2000-(E24-Config!$B$5),IF(G24="Em andamento",1000-MIN(E24-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>3011.99976</v>
+      </c>
+      <c r="L24" s="35">
+        <f>IF(B24="","",IF(I24&lt;&gt;"",1,N(F24)))</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="25">
@@ -6524,6 +6605,10 @@
         <f>IF(OR(B25="",G25="Concluída"),0,IF(G25="Atrasada",3000+MIN(Config!$B$5-E25,60),IF(G25="Vence em breve",2000-(E25-Config!$B$5),IF(G25="Em andamento",1000-MIN(E25-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L25" s="35">
+        <f>IF(B25="","",IF(I25&lt;&gt;"",1,N(F25)))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="32" t="n"/>
@@ -6546,6 +6631,10 @@
         <f>IF(OR(B26="",G26="Concluída"),0,IF(G26="Atrasada",3000+MIN(Config!$B$5-E26,60),IF(G26="Vence em breve",2000-(E26-Config!$B$5),IF(G26="Em andamento",1000-MIN(E26-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L26" s="35">
+        <f>IF(B26="","",IF(I26&lt;&gt;"",1,N(F26)))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="32" t="n"/>
@@ -6568,6 +6657,10 @@
         <f>IF(OR(B27="",G27="Concluída"),0,IF(G27="Atrasada",3000+MIN(Config!$B$5-E27,60),IF(G27="Vence em breve",2000-(E27-Config!$B$5),IF(G27="Em andamento",1000-MIN(E27-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L27" s="35">
+        <f>IF(B27="","",IF(I27&lt;&gt;"",1,N(F27)))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="32" t="n"/>
@@ -6590,6 +6683,10 @@
         <f>IF(OR(B28="",G28="Concluída"),0,IF(G28="Atrasada",3000+MIN(Config!$B$5-E28,60),IF(G28="Vence em breve",2000-(E28-Config!$B$5),IF(G28="Em andamento",1000-MIN(E28-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L28" s="35">
+        <f>IF(B28="","",IF(I28&lt;&gt;"",1,N(F28)))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="32" t="n"/>
@@ -6612,6 +6709,10 @@
         <f>IF(OR(B29="",G29="Concluída"),0,IF(G29="Atrasada",3000+MIN(Config!$B$5-E29,60),IF(G29="Vence em breve",2000-(E29-Config!$B$5),IF(G29="Em andamento",1000-MIN(E29-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L29" s="35">
+        <f>IF(B29="","",IF(I29&lt;&gt;"",1,N(F29)))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="32" t="n"/>
@@ -6634,6 +6735,10 @@
         <f>IF(OR(B30="",G30="Concluída"),0,IF(G30="Atrasada",3000+MIN(Config!$B$5-E30,60),IF(G30="Vence em breve",2000-(E30-Config!$B$5),IF(G30="Em andamento",1000-MIN(E30-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L30" s="35">
+        <f>IF(B30="","",IF(I30&lt;&gt;"",1,N(F30)))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="32" t="n"/>
@@ -6656,6 +6761,10 @@
         <f>IF(OR(B31="",G31="Concluída"),0,IF(G31="Atrasada",3000+MIN(Config!$B$5-E31,60),IF(G31="Vence em breve",2000-(E31-Config!$B$5),IF(G31="Em andamento",1000-MIN(E31-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L31" s="35">
+        <f>IF(B31="","",IF(I31&lt;&gt;"",1,N(F31)))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="32" t="n"/>
@@ -6678,6 +6787,10 @@
         <f>IF(OR(B32="",G32="Concluída"),0,IF(G32="Atrasada",3000+MIN(Config!$B$5-E32,60),IF(G32="Vence em breve",2000-(E32-Config!$B$5),IF(G32="Em andamento",1000-MIN(E32-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L32" s="35">
+        <f>IF(B32="","",IF(I32&lt;&gt;"",1,N(F32)))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="32" t="n"/>
@@ -6700,6 +6813,10 @@
         <f>IF(OR(B33="",G33="Concluída"),0,IF(G33="Atrasada",3000+MIN(Config!$B$5-E33,60),IF(G33="Vence em breve",2000-(E33-Config!$B$5),IF(G33="Em andamento",1000-MIN(E33-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L33" s="35">
+        <f>IF(B33="","",IF(I33&lt;&gt;"",1,N(F33)))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="32" t="n"/>
@@ -6722,6 +6839,10 @@
         <f>IF(OR(B34="",G34="Concluída"),0,IF(G34="Atrasada",3000+MIN(Config!$B$5-E34,60),IF(G34="Vence em breve",2000-(E34-Config!$B$5),IF(G34="Em andamento",1000-MIN(E34-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L34" s="35">
+        <f>IF(B34="","",IF(I34&lt;&gt;"",1,N(F34)))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="32" t="n"/>
@@ -6744,6 +6865,10 @@
         <f>IF(OR(B35="",G35="Concluída"),0,IF(G35="Atrasada",3000+MIN(Config!$B$5-E35,60),IF(G35="Vence em breve",2000-(E35-Config!$B$5),IF(G35="Em andamento",1000-MIN(E35-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L35" s="35">
+        <f>IF(B35="","",IF(I35&lt;&gt;"",1,N(F35)))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="32" t="n"/>
@@ -6766,6 +6891,10 @@
         <f>IF(OR(B36="",G36="Concluída"),0,IF(G36="Atrasada",3000+MIN(Config!$B$5-E36,60),IF(G36="Vence em breve",2000-(E36-Config!$B$5),IF(G36="Em andamento",1000-MIN(E36-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L36" s="35">
+        <f>IF(B36="","",IF(I36&lt;&gt;"",1,N(F36)))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="32" t="n"/>
@@ -6788,6 +6917,10 @@
         <f>IF(OR(B37="",G37="Concluída"),0,IF(G37="Atrasada",3000+MIN(Config!$B$5-E37,60),IF(G37="Vence em breve",2000-(E37-Config!$B$5),IF(G37="Em andamento",1000-MIN(E37-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L37" s="35">
+        <f>IF(B37="","",IF(I37&lt;&gt;"",1,N(F37)))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="32" t="n"/>
@@ -6810,6 +6943,10 @@
         <f>IF(OR(B38="",G38="Concluída"),0,IF(G38="Atrasada",3000+MIN(Config!$B$5-E38,60),IF(G38="Vence em breve",2000-(E38-Config!$B$5),IF(G38="Em andamento",1000-MIN(E38-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L38" s="35">
+        <f>IF(B38="","",IF(I38&lt;&gt;"",1,N(F38)))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="32" t="n"/>
@@ -6832,6 +6969,10 @@
         <f>IF(OR(B39="",G39="Concluída"),0,IF(G39="Atrasada",3000+MIN(Config!$B$5-E39,60),IF(G39="Vence em breve",2000-(E39-Config!$B$5),IF(G39="Em andamento",1000-MIN(E39-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L39" s="35">
+        <f>IF(B39="","",IF(I39&lt;&gt;"",1,N(F39)))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="32" t="n"/>
@@ -6854,6 +6995,10 @@
         <f>IF(OR(B40="",G40="Concluída"),0,IF(G40="Atrasada",3000+MIN(Config!$B$5-E40,60),IF(G40="Vence em breve",2000-(E40-Config!$B$5),IF(G40="Em andamento",1000-MIN(E40-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L40" s="35">
+        <f>IF(B40="","",IF(I40&lt;&gt;"",1,N(F40)))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="32" t="n"/>
@@ -6876,6 +7021,10 @@
         <f>IF(OR(B41="",G41="Concluída"),0,IF(G41="Atrasada",3000+MIN(Config!$B$5-E41,60),IF(G41="Vence em breve",2000-(E41-Config!$B$5),IF(G41="Em andamento",1000-MIN(E41-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L41" s="35">
+        <f>IF(B41="","",IF(I41&lt;&gt;"",1,N(F41)))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="32" t="n"/>
@@ -6898,6 +7047,10 @@
         <f>IF(OR(B42="",G42="Concluída"),0,IF(G42="Atrasada",3000+MIN(Config!$B$5-E42,60),IF(G42="Vence em breve",2000-(E42-Config!$B$5),IF(G42="Em andamento",1000-MIN(E42-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L42" s="35">
+        <f>IF(B42="","",IF(I42&lt;&gt;"",1,N(F42)))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="32" t="n"/>
@@ -6920,6 +7073,10 @@
         <f>IF(OR(B43="",G43="Concluída"),0,IF(G43="Atrasada",3000+MIN(Config!$B$5-E43,60),IF(G43="Vence em breve",2000-(E43-Config!$B$5),IF(G43="Em andamento",1000-MIN(E43-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L43" s="35">
+        <f>IF(B43="","",IF(I43&lt;&gt;"",1,N(F43)))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="32" t="n"/>
@@ -6942,6 +7099,10 @@
         <f>IF(OR(B44="",G44="Concluída"),0,IF(G44="Atrasada",3000+MIN(Config!$B$5-E44,60),IF(G44="Vence em breve",2000-(E44-Config!$B$5),IF(G44="Em andamento",1000-MIN(E44-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L44" s="35">
+        <f>IF(B44="","",IF(I44&lt;&gt;"",1,N(F44)))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="32" t="n"/>
@@ -6964,6 +7125,10 @@
         <f>IF(OR(B45="",G45="Concluída"),0,IF(G45="Atrasada",3000+MIN(Config!$B$5-E45,60),IF(G45="Vence em breve",2000-(E45-Config!$B$5),IF(G45="Em andamento",1000-MIN(E45-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L45" s="35">
+        <f>IF(B45="","",IF(I45&lt;&gt;"",1,N(F45)))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="32" t="n"/>
@@ -6986,6 +7151,10 @@
         <f>IF(OR(B46="",G46="Concluída"),0,IF(G46="Atrasada",3000+MIN(Config!$B$5-E46,60),IF(G46="Vence em breve",2000-(E46-Config!$B$5),IF(G46="Em andamento",1000-MIN(E46-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L46" s="35">
+        <f>IF(B46="","",IF(I46&lt;&gt;"",1,N(F46)))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="32" t="n"/>
@@ -7008,6 +7177,10 @@
         <f>IF(OR(B47="",G47="Concluída"),0,IF(G47="Atrasada",3000+MIN(Config!$B$5-E47,60),IF(G47="Vence em breve",2000-(E47-Config!$B$5),IF(G47="Em andamento",1000-MIN(E47-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L47" s="35">
+        <f>IF(B47="","",IF(I47&lt;&gt;"",1,N(F47)))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="32" t="n"/>
@@ -7030,6 +7203,10 @@
         <f>IF(OR(B48="",G48="Concluída"),0,IF(G48="Atrasada",3000+MIN(Config!$B$5-E48,60),IF(G48="Vence em breve",2000-(E48-Config!$B$5),IF(G48="Em andamento",1000-MIN(E48-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L48" s="35">
+        <f>IF(B48="","",IF(I48&lt;&gt;"",1,N(F48)))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="32" t="n"/>
@@ -7052,6 +7229,10 @@
         <f>IF(OR(B49="",G49="Concluída"),0,IF(G49="Atrasada",3000+MIN(Config!$B$5-E49,60),IF(G49="Vence em breve",2000-(E49-Config!$B$5),IF(G49="Em andamento",1000-MIN(E49-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L49" s="35">
+        <f>IF(B49="","",IF(I49&lt;&gt;"",1,N(F49)))</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="32" t="n"/>
@@ -7074,6 +7255,10 @@
         <f>IF(OR(B50="",G50="Concluída"),0,IF(G50="Atrasada",3000+MIN(Config!$B$5-E50,60),IF(G50="Vence em breve",2000-(E50-Config!$B$5),IF(G50="Em andamento",1000-MIN(E50-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L50" s="35">
+        <f>IF(B50="","",IF(I50&lt;&gt;"",1,N(F50)))</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="32" t="n"/>
@@ -7096,6 +7281,10 @@
         <f>IF(OR(B51="",G51="Concluída"),0,IF(G51="Atrasada",3000+MIN(Config!$B$5-E51,60),IF(G51="Vence em breve",2000-(E51-Config!$B$5),IF(G51="Em andamento",1000-MIN(E51-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L51" s="35">
+        <f>IF(B51="","",IF(I51&lt;&gt;"",1,N(F51)))</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="32" t="n"/>
@@ -7118,6 +7307,10 @@
         <f>IF(OR(B52="",G52="Concluída"),0,IF(G52="Atrasada",3000+MIN(Config!$B$5-E52,60),IF(G52="Vence em breve",2000-(E52-Config!$B$5),IF(G52="Em andamento",1000-MIN(E52-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L52" s="35">
+        <f>IF(B52="","",IF(I52&lt;&gt;"",1,N(F52)))</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="32" t="n"/>
@@ -7140,6 +7333,10 @@
         <f>IF(OR(B53="",G53="Concluída"),0,IF(G53="Atrasada",3000+MIN(Config!$B$5-E53,60),IF(G53="Vence em breve",2000-(E53-Config!$B$5),IF(G53="Em andamento",1000-MIN(E53-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L53" s="35">
+        <f>IF(B53="","",IF(I53&lt;&gt;"",1,N(F53)))</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="32" t="n"/>
@@ -7162,6 +7359,10 @@
         <f>IF(OR(B54="",G54="Concluída"),0,IF(G54="Atrasada",3000+MIN(Config!$B$5-E54,60),IF(G54="Vence em breve",2000-(E54-Config!$B$5),IF(G54="Em andamento",1000-MIN(E54-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L54" s="35">
+        <f>IF(B54="","",IF(I54&lt;&gt;"",1,N(F54)))</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="32" t="n"/>
@@ -7184,6 +7385,10 @@
         <f>IF(OR(B55="",G55="Concluída"),0,IF(G55="Atrasada",3000+MIN(Config!$B$5-E55,60),IF(G55="Vence em breve",2000-(E55-Config!$B$5),IF(G55="Em andamento",1000-MIN(E55-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L55" s="35">
+        <f>IF(B55="","",IF(I55&lt;&gt;"",1,N(F55)))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="32" t="n"/>
@@ -7206,6 +7411,10 @@
         <f>IF(OR(B56="",G56="Concluída"),0,IF(G56="Atrasada",3000+MIN(Config!$B$5-E56,60),IF(G56="Vence em breve",2000-(E56-Config!$B$5),IF(G56="Em andamento",1000-MIN(E56-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L56" s="35">
+        <f>IF(B56="","",IF(I56&lt;&gt;"",1,N(F56)))</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="32" t="n"/>
@@ -7228,6 +7437,10 @@
         <f>IF(OR(B57="",G57="Concluída"),0,IF(G57="Atrasada",3000+MIN(Config!$B$5-E57,60),IF(G57="Vence em breve",2000-(E57-Config!$B$5),IF(G57="Em andamento",1000-MIN(E57-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L57" s="35">
+        <f>IF(B57="","",IF(I57&lt;&gt;"",1,N(F57)))</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="32" t="n"/>
@@ -7250,6 +7463,10 @@
         <f>IF(OR(B58="",G58="Concluída"),0,IF(G58="Atrasada",3000+MIN(Config!$B$5-E58,60),IF(G58="Vence em breve",2000-(E58-Config!$B$5),IF(G58="Em andamento",1000-MIN(E58-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L58" s="35">
+        <f>IF(B58="","",IF(I58&lt;&gt;"",1,N(F58)))</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="32" t="n"/>
@@ -7272,6 +7489,10 @@
         <f>IF(OR(B59="",G59="Concluída"),0,IF(G59="Atrasada",3000+MIN(Config!$B$5-E59,60),IF(G59="Vence em breve",2000-(E59-Config!$B$5),IF(G59="Em andamento",1000-MIN(E59-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L59" s="35">
+        <f>IF(B59="","",IF(I59&lt;&gt;"",1,N(F59)))</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="32" t="n"/>
@@ -7294,6 +7515,10 @@
         <f>IF(OR(B60="",G60="Concluída"),0,IF(G60="Atrasada",3000+MIN(Config!$B$5-E60,60),IF(G60="Vence em breve",2000-(E60-Config!$B$5),IF(G60="Em andamento",1000-MIN(E60-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L60" s="35">
+        <f>IF(B60="","",IF(I60&lt;&gt;"",1,N(F60)))</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="32" t="n"/>
@@ -7316,6 +7541,10 @@
         <f>IF(OR(B61="",G61="Concluída"),0,IF(G61="Atrasada",3000+MIN(Config!$B$5-E61,60),IF(G61="Vence em breve",2000-(E61-Config!$B$5),IF(G61="Em andamento",1000-MIN(E61-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L61" s="35">
+        <f>IF(B61="","",IF(I61&lt;&gt;"",1,N(F61)))</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="32" t="n"/>
@@ -7338,6 +7567,10 @@
         <f>IF(OR(B62="",G62="Concluída"),0,IF(G62="Atrasada",3000+MIN(Config!$B$5-E62,60),IF(G62="Vence em breve",2000-(E62-Config!$B$5),IF(G62="Em andamento",1000-MIN(E62-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L62" s="35">
+        <f>IF(B62="","",IF(I62&lt;&gt;"",1,N(F62)))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="32" t="n"/>
@@ -7360,6 +7593,10 @@
         <f>IF(OR(B63="",G63="Concluída"),0,IF(G63="Atrasada",3000+MIN(Config!$B$5-E63,60),IF(G63="Vence em breve",2000-(E63-Config!$B$5),IF(G63="Em andamento",1000-MIN(E63-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L63" s="35">
+        <f>IF(B63="","",IF(I63&lt;&gt;"",1,N(F63)))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="32" t="n"/>
@@ -7382,6 +7619,10 @@
         <f>IF(OR(B64="",G64="Concluída"),0,IF(G64="Atrasada",3000+MIN(Config!$B$5-E64,60),IF(G64="Vence em breve",2000-(E64-Config!$B$5),IF(G64="Em andamento",1000-MIN(E64-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L64" s="35">
+        <f>IF(B64="","",IF(I64&lt;&gt;"",1,N(F64)))</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="32" t="n"/>
@@ -7404,6 +7645,10 @@
         <f>IF(OR(B65="",G65="Concluída"),0,IF(G65="Atrasada",3000+MIN(Config!$B$5-E65,60),IF(G65="Vence em breve",2000-(E65-Config!$B$5),IF(G65="Em andamento",1000-MIN(E65-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L65" s="35">
+        <f>IF(B65="","",IF(I65&lt;&gt;"",1,N(F65)))</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="32" t="n"/>
@@ -7426,6 +7671,10 @@
         <f>IF(OR(B66="",G66="Concluída"),0,IF(G66="Atrasada",3000+MIN(Config!$B$5-E66,60),IF(G66="Vence em breve",2000-(E66-Config!$B$5),IF(G66="Em andamento",1000-MIN(E66-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L66" s="35">
+        <f>IF(B66="","",IF(I66&lt;&gt;"",1,N(F66)))</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="32" t="n"/>
@@ -7448,6 +7697,10 @@
         <f>IF(OR(B67="",G67="Concluída"),0,IF(G67="Atrasada",3000+MIN(Config!$B$5-E67,60),IF(G67="Vence em breve",2000-(E67-Config!$B$5),IF(G67="Em andamento",1000-MIN(E67-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L67" s="35">
+        <f>IF(B67="","",IF(I67&lt;&gt;"",1,N(F67)))</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="32" t="n"/>
@@ -7470,6 +7723,10 @@
         <f>IF(OR(B68="",G68="Concluída"),0,IF(G68="Atrasada",3000+MIN(Config!$B$5-E68,60),IF(G68="Vence em breve",2000-(E68-Config!$B$5),IF(G68="Em andamento",1000-MIN(E68-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L68" s="35">
+        <f>IF(B68="","",IF(I68&lt;&gt;"",1,N(F68)))</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="32" t="n"/>
@@ -7492,6 +7749,10 @@
         <f>IF(OR(B69="",G69="Concluída"),0,IF(G69="Atrasada",3000+MIN(Config!$B$5-E69,60),IF(G69="Vence em breve",2000-(E69-Config!$B$5),IF(G69="Em andamento",1000-MIN(E69-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L69" s="35">
+        <f>IF(B69="","",IF(I69&lt;&gt;"",1,N(F69)))</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="32" t="n"/>
@@ -7514,6 +7775,10 @@
         <f>IF(OR(B70="",G70="Concluída"),0,IF(G70="Atrasada",3000+MIN(Config!$B$5-E70,60),IF(G70="Vence em breve",2000-(E70-Config!$B$5),IF(G70="Em andamento",1000-MIN(E70-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L70" s="35">
+        <f>IF(B70="","",IF(I70&lt;&gt;"",1,N(F70)))</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="32" t="n"/>
@@ -7536,6 +7801,10 @@
         <f>IF(OR(B71="",G71="Concluída"),0,IF(G71="Atrasada",3000+MIN(Config!$B$5-E71,60),IF(G71="Vence em breve",2000-(E71-Config!$B$5),IF(G71="Em andamento",1000-MIN(E71-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L71" s="35">
+        <f>IF(B71="","",IF(I71&lt;&gt;"",1,N(F71)))</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="32" t="n"/>
@@ -7558,6 +7827,10 @@
         <f>IF(OR(B72="",G72="Concluída"),0,IF(G72="Atrasada",3000+MIN(Config!$B$5-E72,60),IF(G72="Vence em breve",2000-(E72-Config!$B$5),IF(G72="Em andamento",1000-MIN(E72-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L72" s="35">
+        <f>IF(B72="","",IF(I72&lt;&gt;"",1,N(F72)))</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="32" t="n"/>
@@ -7580,6 +7853,10 @@
         <f>IF(OR(B73="",G73="Concluída"),0,IF(G73="Atrasada",3000+MIN(Config!$B$5-E73,60),IF(G73="Vence em breve",2000-(E73-Config!$B$5),IF(G73="Em andamento",1000-MIN(E73-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L73" s="35">
+        <f>IF(B73="","",IF(I73&lt;&gt;"",1,N(F73)))</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="32" t="n"/>
@@ -7602,6 +7879,10 @@
         <f>IF(OR(B74="",G74="Concluída"),0,IF(G74="Atrasada",3000+MIN(Config!$B$5-E74,60),IF(G74="Vence em breve",2000-(E74-Config!$B$5),IF(G74="Em andamento",1000-MIN(E74-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L74" s="35">
+        <f>IF(B74="","",IF(I74&lt;&gt;"",1,N(F74)))</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="32" t="n"/>
@@ -7624,6 +7905,10 @@
         <f>IF(OR(B75="",G75="Concluída"),0,IF(G75="Atrasada",3000+MIN(Config!$B$5-E75,60),IF(G75="Vence em breve",2000-(E75-Config!$B$5),IF(G75="Em andamento",1000-MIN(E75-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L75" s="35">
+        <f>IF(B75="","",IF(I75&lt;&gt;"",1,N(F75)))</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="32" t="n"/>
@@ -7646,6 +7931,10 @@
         <f>IF(OR(B76="",G76="Concluída"),0,IF(G76="Atrasada",3000+MIN(Config!$B$5-E76,60),IF(G76="Vence em breve",2000-(E76-Config!$B$5),IF(G76="Em andamento",1000-MIN(E76-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L76" s="35">
+        <f>IF(B76="","",IF(I76&lt;&gt;"",1,N(F76)))</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="32" t="n"/>
@@ -7668,6 +7957,10 @@
         <f>IF(OR(B77="",G77="Concluída"),0,IF(G77="Atrasada",3000+MIN(Config!$B$5-E77,60),IF(G77="Vence em breve",2000-(E77-Config!$B$5),IF(G77="Em andamento",1000-MIN(E77-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L77" s="35">
+        <f>IF(B77="","",IF(I77&lt;&gt;"",1,N(F77)))</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="32" t="n"/>
@@ -7690,6 +7983,10 @@
         <f>IF(OR(B78="",G78="Concluída"),0,IF(G78="Atrasada",3000+MIN(Config!$B$5-E78,60),IF(G78="Vence em breve",2000-(E78-Config!$B$5),IF(G78="Em andamento",1000-MIN(E78-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L78" s="35">
+        <f>IF(B78="","",IF(I78&lt;&gt;"",1,N(F78)))</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="32" t="n"/>
@@ -7712,6 +8009,10 @@
         <f>IF(OR(B79="",G79="Concluída"),0,IF(G79="Atrasada",3000+MIN(Config!$B$5-E79,60),IF(G79="Vence em breve",2000-(E79-Config!$B$5),IF(G79="Em andamento",1000-MIN(E79-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L79" s="35">
+        <f>IF(B79="","",IF(I79&lt;&gt;"",1,N(F79)))</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="32" t="n"/>
@@ -7734,6 +8035,10 @@
         <f>IF(OR(B80="",G80="Concluída"),0,IF(G80="Atrasada",3000+MIN(Config!$B$5-E80,60),IF(G80="Vence em breve",2000-(E80-Config!$B$5),IF(G80="Em andamento",1000-MIN(E80-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L80" s="35">
+        <f>IF(B80="","",IF(I80&lt;&gt;"",1,N(F80)))</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="32" t="n"/>
@@ -7756,6 +8061,10 @@
         <f>IF(OR(B81="",G81="Concluída"),0,IF(G81="Atrasada",3000+MIN(Config!$B$5-E81,60),IF(G81="Vence em breve",2000-(E81-Config!$B$5),IF(G81="Em andamento",1000-MIN(E81-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L81" s="35">
+        <f>IF(B81="","",IF(I81&lt;&gt;"",1,N(F81)))</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="32" t="n"/>
@@ -7778,6 +8087,10 @@
         <f>IF(OR(B82="",G82="Concluída"),0,IF(G82="Atrasada",3000+MIN(Config!$B$5-E82,60),IF(G82="Vence em breve",2000-(E82-Config!$B$5),IF(G82="Em andamento",1000-MIN(E82-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L82" s="35">
+        <f>IF(B82="","",IF(I82&lt;&gt;"",1,N(F82)))</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="32" t="n"/>
@@ -7800,6 +8113,10 @@
         <f>IF(OR(B83="",G83="Concluída"),0,IF(G83="Atrasada",3000+MIN(Config!$B$5-E83,60),IF(G83="Vence em breve",2000-(E83-Config!$B$5),IF(G83="Em andamento",1000-MIN(E83-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L83" s="35">
+        <f>IF(B83="","",IF(I83&lt;&gt;"",1,N(F83)))</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="32" t="n"/>
@@ -7822,6 +8139,10 @@
         <f>IF(OR(B84="",G84="Concluída"),0,IF(G84="Atrasada",3000+MIN(Config!$B$5-E84,60),IF(G84="Vence em breve",2000-(E84-Config!$B$5),IF(G84="Em andamento",1000-MIN(E84-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L84" s="35">
+        <f>IF(B84="","",IF(I84&lt;&gt;"",1,N(F84)))</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="32" t="n"/>
@@ -7844,6 +8165,10 @@
         <f>IF(OR(B85="",G85="Concluída"),0,IF(G85="Atrasada",3000+MIN(Config!$B$5-E85,60),IF(G85="Vence em breve",2000-(E85-Config!$B$5),IF(G85="Em andamento",1000-MIN(E85-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L85" s="35">
+        <f>IF(B85="","",IF(I85&lt;&gt;"",1,N(F85)))</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="32" t="n"/>
@@ -7866,6 +8191,10 @@
         <f>IF(OR(B86="",G86="Concluída"),0,IF(G86="Atrasada",3000+MIN(Config!$B$5-E86,60),IF(G86="Vence em breve",2000-(E86-Config!$B$5),IF(G86="Em andamento",1000-MIN(E86-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L86" s="35">
+        <f>IF(B86="","",IF(I86&lt;&gt;"",1,N(F86)))</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="32" t="n"/>
@@ -7888,6 +8217,10 @@
         <f>IF(OR(B87="",G87="Concluída"),0,IF(G87="Atrasada",3000+MIN(Config!$B$5-E87,60),IF(G87="Vence em breve",2000-(E87-Config!$B$5),IF(G87="Em andamento",1000-MIN(E87-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L87" s="35">
+        <f>IF(B87="","",IF(I87&lt;&gt;"",1,N(F87)))</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="32" t="n"/>
@@ -7910,6 +8243,10 @@
         <f>IF(OR(B88="",G88="Concluída"),0,IF(G88="Atrasada",3000+MIN(Config!$B$5-E88,60),IF(G88="Vence em breve",2000-(E88-Config!$B$5),IF(G88="Em andamento",1000-MIN(E88-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L88" s="35">
+        <f>IF(B88="","",IF(I88&lt;&gt;"",1,N(F88)))</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="32" t="n"/>
@@ -7932,6 +8269,10 @@
         <f>IF(OR(B89="",G89="Concluída"),0,IF(G89="Atrasada",3000+MIN(Config!$B$5-E89,60),IF(G89="Vence em breve",2000-(E89-Config!$B$5),IF(G89="Em andamento",1000-MIN(E89-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L89" s="35">
+        <f>IF(B89="","",IF(I89&lt;&gt;"",1,N(F89)))</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="32" t="n"/>
@@ -7954,6 +8295,10 @@
         <f>IF(OR(B90="",G90="Concluída"),0,IF(G90="Atrasada",3000+MIN(Config!$B$5-E90,60),IF(G90="Vence em breve",2000-(E90-Config!$B$5),IF(G90="Em andamento",1000-MIN(E90-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L90" s="35">
+        <f>IF(B90="","",IF(I90&lt;&gt;"",1,N(F90)))</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="32" t="n"/>
@@ -7976,6 +8321,10 @@
         <f>IF(OR(B91="",G91="Concluída"),0,IF(G91="Atrasada",3000+MIN(Config!$B$5-E91,60),IF(G91="Vence em breve",2000-(E91-Config!$B$5),IF(G91="Em andamento",1000-MIN(E91-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L91" s="35">
+        <f>IF(B91="","",IF(I91&lt;&gt;"",1,N(F91)))</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="32" t="n"/>
@@ -7998,6 +8347,10 @@
         <f>IF(OR(B92="",G92="Concluída"),0,IF(G92="Atrasada",3000+MIN(Config!$B$5-E92,60),IF(G92="Vence em breve",2000-(E92-Config!$B$5),IF(G92="Em andamento",1000-MIN(E92-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L92" s="35">
+        <f>IF(B92="","",IF(I92&lt;&gt;"",1,N(F92)))</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="32" t="n"/>
@@ -8020,6 +8373,10 @@
         <f>IF(OR(B93="",G93="Concluída"),0,IF(G93="Atrasada",3000+MIN(Config!$B$5-E93,60),IF(G93="Vence em breve",2000-(E93-Config!$B$5),IF(G93="Em andamento",1000-MIN(E93-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L93" s="35">
+        <f>IF(B93="","",IF(I93&lt;&gt;"",1,N(F93)))</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="32" t="n"/>
@@ -8042,6 +8399,10 @@
         <f>IF(OR(B94="",G94="Concluída"),0,IF(G94="Atrasada",3000+MIN(Config!$B$5-E94,60),IF(G94="Vence em breve",2000-(E94-Config!$B$5),IF(G94="Em andamento",1000-MIN(E94-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L94" s="35">
+        <f>IF(B94="","",IF(I94&lt;&gt;"",1,N(F94)))</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="32" t="n"/>
@@ -8064,6 +8425,10 @@
         <f>IF(OR(B95="",G95="Concluída"),0,IF(G95="Atrasada",3000+MIN(Config!$B$5-E95,60),IF(G95="Vence em breve",2000-(E95-Config!$B$5),IF(G95="Em andamento",1000-MIN(E95-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L95" s="35">
+        <f>IF(B95="","",IF(I95&lt;&gt;"",1,N(F95)))</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="32" t="n"/>
@@ -8086,6 +8451,10 @@
         <f>IF(OR(B96="",G96="Concluída"),0,IF(G96="Atrasada",3000+MIN(Config!$B$5-E96,60),IF(G96="Vence em breve",2000-(E96-Config!$B$5),IF(G96="Em andamento",1000-MIN(E96-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L96" s="35">
+        <f>IF(B96="","",IF(I96&lt;&gt;"",1,N(F96)))</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="32" t="n"/>
@@ -8108,6 +8477,10 @@
         <f>IF(OR(B97="",G97="Concluída"),0,IF(G97="Atrasada",3000+MIN(Config!$B$5-E97,60),IF(G97="Vence em breve",2000-(E97-Config!$B$5),IF(G97="Em andamento",1000-MIN(E97-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L97" s="35">
+        <f>IF(B97="","",IF(I97&lt;&gt;"",1,N(F97)))</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="32" t="n"/>
@@ -8130,6 +8503,10 @@
         <f>IF(OR(B98="",G98="Concluída"),0,IF(G98="Atrasada",3000+MIN(Config!$B$5-E98,60),IF(G98="Vence em breve",2000-(E98-Config!$B$5),IF(G98="Em andamento",1000-MIN(E98-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L98" s="35">
+        <f>IF(B98="","",IF(I98&lt;&gt;"",1,N(F98)))</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="32" t="n"/>
@@ -8152,6 +8529,10 @@
         <f>IF(OR(B99="",G99="Concluída"),0,IF(G99="Atrasada",3000+MIN(Config!$B$5-E99,60),IF(G99="Vence em breve",2000-(E99-Config!$B$5),IF(G99="Em andamento",1000-MIN(E99-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L99" s="35">
+        <f>IF(B99="","",IF(I99&lt;&gt;"",1,N(F99)))</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="32" t="n"/>
@@ -8174,6 +8555,10 @@
         <f>IF(OR(B100="",G100="Concluída"),0,IF(G100="Atrasada",3000+MIN(Config!$B$5-E100,60),IF(G100="Vence em breve",2000-(E100-Config!$B$5),IF(G100="Em andamento",1000-MIN(E100-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L100" s="35">
+        <f>IF(B100="","",IF(I100&lt;&gt;"",1,N(F100)))</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="32" t="n"/>
@@ -8196,6 +8581,10 @@
         <f>IF(OR(B101="",G101="Concluída"),0,IF(G101="Atrasada",3000+MIN(Config!$B$5-E101,60),IF(G101="Vence em breve",2000-(E101-Config!$B$5),IF(G101="Em andamento",1000-MIN(E101-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L101" s="35">
+        <f>IF(B101="","",IF(I101&lt;&gt;"",1,N(F101)))</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="32" t="n"/>
@@ -8218,6 +8607,10 @@
         <f>IF(OR(B102="",G102="Concluída"),0,IF(G102="Atrasada",3000+MIN(Config!$B$5-E102,60),IF(G102="Vence em breve",2000-(E102-Config!$B$5),IF(G102="Em andamento",1000-MIN(E102-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L102" s="35">
+        <f>IF(B102="","",IF(I102&lt;&gt;"",1,N(F102)))</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="32" t="n"/>
@@ -8240,6 +8633,10 @@
         <f>IF(OR(B103="",G103="Concluída"),0,IF(G103="Atrasada",3000+MIN(Config!$B$5-E103,60),IF(G103="Vence em breve",2000-(E103-Config!$B$5),IF(G103="Em andamento",1000-MIN(E103-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L103" s="35">
+        <f>IF(B103="","",IF(I103&lt;&gt;"",1,N(F103)))</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="32" t="n"/>
@@ -8262,6 +8659,10 @@
         <f>IF(OR(B104="",G104="Concluída"),0,IF(G104="Atrasada",3000+MIN(Config!$B$5-E104,60),IF(G104="Vence em breve",2000-(E104-Config!$B$5),IF(G104="Em andamento",1000-MIN(E104-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L104" s="35">
+        <f>IF(B104="","",IF(I104&lt;&gt;"",1,N(F104)))</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="32" t="n"/>
@@ -8284,6 +8685,10 @@
         <f>IF(OR(B105="",G105="Concluída"),0,IF(G105="Atrasada",3000+MIN(Config!$B$5-E105,60),IF(G105="Vence em breve",2000-(E105-Config!$B$5),IF(G105="Em andamento",1000-MIN(E105-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L105" s="35">
+        <f>IF(B105="","",IF(I105&lt;&gt;"",1,N(F105)))</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="32" t="n"/>
@@ -8306,6 +8711,10 @@
         <f>IF(OR(B106="",G106="Concluída"),0,IF(G106="Atrasada",3000+MIN(Config!$B$5-E106,60),IF(G106="Vence em breve",2000-(E106-Config!$B$5),IF(G106="Em andamento",1000-MIN(E106-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L106" s="35">
+        <f>IF(B106="","",IF(I106&lt;&gt;"",1,N(F106)))</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="32" t="n"/>
@@ -8328,6 +8737,10 @@
         <f>IF(OR(B107="",G107="Concluída"),0,IF(G107="Atrasada",3000+MIN(Config!$B$5-E107,60),IF(G107="Vence em breve",2000-(E107-Config!$B$5),IF(G107="Em andamento",1000-MIN(E107-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L107" s="35">
+        <f>IF(B107="","",IF(I107&lt;&gt;"",1,N(F107)))</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="32" t="n"/>
@@ -8350,6 +8763,10 @@
         <f>IF(OR(B108="",G108="Concluída"),0,IF(G108="Atrasada",3000+MIN(Config!$B$5-E108,60),IF(G108="Vence em breve",2000-(E108-Config!$B$5),IF(G108="Em andamento",1000-MIN(E108-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L108" s="35">
+        <f>IF(B108="","",IF(I108&lt;&gt;"",1,N(F108)))</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="32" t="n"/>
@@ -8372,6 +8789,10 @@
         <f>IF(OR(B109="",G109="Concluída"),0,IF(G109="Atrasada",3000+MIN(Config!$B$5-E109,60),IF(G109="Vence em breve",2000-(E109-Config!$B$5),IF(G109="Em andamento",1000-MIN(E109-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L109" s="35">
+        <f>IF(B109="","",IF(I109&lt;&gt;"",1,N(F109)))</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="32" t="n"/>
@@ -8394,6 +8815,10 @@
         <f>IF(OR(B110="",G110="Concluída"),0,IF(G110="Atrasada",3000+MIN(Config!$B$5-E110,60),IF(G110="Vence em breve",2000-(E110-Config!$B$5),IF(G110="Em andamento",1000-MIN(E110-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L110" s="35">
+        <f>IF(B110="","",IF(I110&lt;&gt;"",1,N(F110)))</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="32" t="n"/>
@@ -8416,6 +8841,10 @@
         <f>IF(OR(B111="",G111="Concluída"),0,IF(G111="Atrasada",3000+MIN(Config!$B$5-E111,60),IF(G111="Vence em breve",2000-(E111-Config!$B$5),IF(G111="Em andamento",1000-MIN(E111-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L111" s="35">
+        <f>IF(B111="","",IF(I111&lt;&gt;"",1,N(F111)))</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="32" t="n"/>
@@ -8438,6 +8867,10 @@
         <f>IF(OR(B112="",G112="Concluída"),0,IF(G112="Atrasada",3000+MIN(Config!$B$5-E112,60),IF(G112="Vence em breve",2000-(E112-Config!$B$5),IF(G112="Em andamento",1000-MIN(E112-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L112" s="35">
+        <f>IF(B112="","",IF(I112&lt;&gt;"",1,N(F112)))</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="32" t="n"/>
@@ -8460,6 +8893,10 @@
         <f>IF(OR(B113="",G113="Concluída"),0,IF(G113="Atrasada",3000+MIN(Config!$B$5-E113,60),IF(G113="Vence em breve",2000-(E113-Config!$B$5),IF(G113="Em andamento",1000-MIN(E113-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L113" s="35">
+        <f>IF(B113="","",IF(I113&lt;&gt;"",1,N(F113)))</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="32" t="n"/>
@@ -8482,6 +8919,10 @@
         <f>IF(OR(B114="",G114="Concluída"),0,IF(G114="Atrasada",3000+MIN(Config!$B$5-E114,60),IF(G114="Vence em breve",2000-(E114-Config!$B$5),IF(G114="Em andamento",1000-MIN(E114-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L114" s="35">
+        <f>IF(B114="","",IF(I114&lt;&gt;"",1,N(F114)))</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="32" t="n"/>
@@ -8504,6 +8945,10 @@
         <f>IF(OR(B115="",G115="Concluída"),0,IF(G115="Atrasada",3000+MIN(Config!$B$5-E115,60),IF(G115="Vence em breve",2000-(E115-Config!$B$5),IF(G115="Em andamento",1000-MIN(E115-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L115" s="35">
+        <f>IF(B115="","",IF(I115&lt;&gt;"",1,N(F115)))</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="32" t="n"/>
@@ -8526,6 +8971,10 @@
         <f>IF(OR(B116="",G116="Concluída"),0,IF(G116="Atrasada",3000+MIN(Config!$B$5-E116,60),IF(G116="Vence em breve",2000-(E116-Config!$B$5),IF(G116="Em andamento",1000-MIN(E116-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L116" s="35">
+        <f>IF(B116="","",IF(I116&lt;&gt;"",1,N(F116)))</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="32" t="n"/>
@@ -8548,6 +8997,10 @@
         <f>IF(OR(B117="",G117="Concluída"),0,IF(G117="Atrasada",3000+MIN(Config!$B$5-E117,60),IF(G117="Vence em breve",2000-(E117-Config!$B$5),IF(G117="Em andamento",1000-MIN(E117-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L117" s="35">
+        <f>IF(B117="","",IF(I117&lt;&gt;"",1,N(F117)))</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="32" t="n"/>
@@ -8570,6 +9023,10 @@
         <f>IF(OR(B118="",G118="Concluída"),0,IF(G118="Atrasada",3000+MIN(Config!$B$5-E118,60),IF(G118="Vence em breve",2000-(E118-Config!$B$5),IF(G118="Em andamento",1000-MIN(E118-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L118" s="35">
+        <f>IF(B118="","",IF(I118&lt;&gt;"",1,N(F118)))</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="32" t="n"/>
@@ -8592,6 +9049,10 @@
         <f>IF(OR(B119="",G119="Concluída"),0,IF(G119="Atrasada",3000+MIN(Config!$B$5-E119,60),IF(G119="Vence em breve",2000-(E119-Config!$B$5),IF(G119="Em andamento",1000-MIN(E119-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L119" s="35">
+        <f>IF(B119="","",IF(I119&lt;&gt;"",1,N(F119)))</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="32" t="n"/>
@@ -8614,6 +9075,10 @@
         <f>IF(OR(B120="",G120="Concluída"),0,IF(G120="Atrasada",3000+MIN(Config!$B$5-E120,60),IF(G120="Vence em breve",2000-(E120-Config!$B$5),IF(G120="Em andamento",1000-MIN(E120-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L120" s="35">
+        <f>IF(B120="","",IF(I120&lt;&gt;"",1,N(F120)))</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="32" t="n"/>
@@ -8636,6 +9101,10 @@
         <f>IF(OR(B121="",G121="Concluída"),0,IF(G121="Atrasada",3000+MIN(Config!$B$5-E121,60),IF(G121="Vence em breve",2000-(E121-Config!$B$5),IF(G121="Em andamento",1000-MIN(E121-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L121" s="35">
+        <f>IF(B121="","",IF(I121&lt;&gt;"",1,N(F121)))</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="32" t="n"/>
@@ -8658,6 +9127,10 @@
         <f>IF(OR(B122="",G122="Concluída"),0,IF(G122="Atrasada",3000+MIN(Config!$B$5-E122,60),IF(G122="Vence em breve",2000-(E122-Config!$B$5),IF(G122="Em andamento",1000-MIN(E122-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L122" s="35">
+        <f>IF(B122="","",IF(I122&lt;&gt;"",1,N(F122)))</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="32" t="n"/>
@@ -8680,6 +9153,10 @@
         <f>IF(OR(B123="",G123="Concluída"),0,IF(G123="Atrasada",3000+MIN(Config!$B$5-E123,60),IF(G123="Vence em breve",2000-(E123-Config!$B$5),IF(G123="Em andamento",1000-MIN(E123-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L123" s="35">
+        <f>IF(B123="","",IF(I123&lt;&gt;"",1,N(F123)))</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="32" t="n"/>
@@ -8702,6 +9179,10 @@
         <f>IF(OR(B124="",G124="Concluída"),0,IF(G124="Atrasada",3000+MIN(Config!$B$5-E124,60),IF(G124="Vence em breve",2000-(E124-Config!$B$5),IF(G124="Em andamento",1000-MIN(E124-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L124" s="35">
+        <f>IF(B124="","",IF(I124&lt;&gt;"",1,N(F124)))</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="32" t="n"/>
@@ -8724,6 +9205,10 @@
         <f>IF(OR(B125="",G125="Concluída"),0,IF(G125="Atrasada",3000+MIN(Config!$B$5-E125,60),IF(G125="Vence em breve",2000-(E125-Config!$B$5),IF(G125="Em andamento",1000-MIN(E125-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L125" s="35">
+        <f>IF(B125="","",IF(I125&lt;&gt;"",1,N(F125)))</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="32" t="n"/>
@@ -8746,6 +9231,10 @@
         <f>IF(OR(B126="",G126="Concluída"),0,IF(G126="Atrasada",3000+MIN(Config!$B$5-E126,60),IF(G126="Vence em breve",2000-(E126-Config!$B$5),IF(G126="Em andamento",1000-MIN(E126-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L126" s="35">
+        <f>IF(B126="","",IF(I126&lt;&gt;"",1,N(F126)))</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="32" t="n"/>
@@ -8768,6 +9257,10 @@
         <f>IF(OR(B127="",G127="Concluída"),0,IF(G127="Atrasada",3000+MIN(Config!$B$5-E127,60),IF(G127="Vence em breve",2000-(E127-Config!$B$5),IF(G127="Em andamento",1000-MIN(E127-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L127" s="35">
+        <f>IF(B127="","",IF(I127&lt;&gt;"",1,N(F127)))</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="32" t="n"/>
@@ -8790,6 +9283,10 @@
         <f>IF(OR(B128="",G128="Concluída"),0,IF(G128="Atrasada",3000+MIN(Config!$B$5-E128,60),IF(G128="Vence em breve",2000-(E128-Config!$B$5),IF(G128="Em andamento",1000-MIN(E128-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L128" s="35">
+        <f>IF(B128="","",IF(I128&lt;&gt;"",1,N(F128)))</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="32" t="n"/>
@@ -8812,6 +9309,10 @@
         <f>IF(OR(B129="",G129="Concluída"),0,IF(G129="Atrasada",3000+MIN(Config!$B$5-E129,60),IF(G129="Vence em breve",2000-(E129-Config!$B$5),IF(G129="Em andamento",1000-MIN(E129-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L129" s="35">
+        <f>IF(B129="","",IF(I129&lt;&gt;"",1,N(F129)))</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="32" t="n"/>
@@ -8834,6 +9335,10 @@
         <f>IF(OR(B130="",G130="Concluída"),0,IF(G130="Atrasada",3000+MIN(Config!$B$5-E130,60),IF(G130="Vence em breve",2000-(E130-Config!$B$5),IF(G130="Em andamento",1000-MIN(E130-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L130" s="35">
+        <f>IF(B130="","",IF(I130&lt;&gt;"",1,N(F130)))</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="32" t="n"/>
@@ -8856,6 +9361,10 @@
         <f>IF(OR(B131="",G131="Concluída"),0,IF(G131="Atrasada",3000+MIN(Config!$B$5-E131,60),IF(G131="Vence em breve",2000-(E131-Config!$B$5),IF(G131="Em andamento",1000-MIN(E131-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L131" s="35">
+        <f>IF(B131="","",IF(I131&lt;&gt;"",1,N(F131)))</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="32" t="n"/>
@@ -8878,6 +9387,10 @@
         <f>IF(OR(B132="",G132="Concluída"),0,IF(G132="Atrasada",3000+MIN(Config!$B$5-E132,60),IF(G132="Vence em breve",2000-(E132-Config!$B$5),IF(G132="Em andamento",1000-MIN(E132-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L132" s="35">
+        <f>IF(B132="","",IF(I132&lt;&gt;"",1,N(F132)))</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="32" t="n"/>
@@ -8900,6 +9413,10 @@
         <f>IF(OR(B133="",G133="Concluída"),0,IF(G133="Atrasada",3000+MIN(Config!$B$5-E133,60),IF(G133="Vence em breve",2000-(E133-Config!$B$5),IF(G133="Em andamento",1000-MIN(E133-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L133" s="35">
+        <f>IF(B133="","",IF(I133&lt;&gt;"",1,N(F133)))</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="32" t="n"/>
@@ -8922,6 +9439,10 @@
         <f>IF(OR(B134="",G134="Concluída"),0,IF(G134="Atrasada",3000+MIN(Config!$B$5-E134,60),IF(G134="Vence em breve",2000-(E134-Config!$B$5),IF(G134="Em andamento",1000-MIN(E134-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L134" s="35">
+        <f>IF(B134="","",IF(I134&lt;&gt;"",1,N(F134)))</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="32" t="n"/>
@@ -8944,6 +9465,10 @@
         <f>IF(OR(B135="",G135="Concluída"),0,IF(G135="Atrasada",3000+MIN(Config!$B$5-E135,60),IF(G135="Vence em breve",2000-(E135-Config!$B$5),IF(G135="Em andamento",1000-MIN(E135-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L135" s="35">
+        <f>IF(B135="","",IF(I135&lt;&gt;"",1,N(F135)))</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="32" t="n"/>
@@ -8966,6 +9491,10 @@
         <f>IF(OR(B136="",G136="Concluída"),0,IF(G136="Atrasada",3000+MIN(Config!$B$5-E136,60),IF(G136="Vence em breve",2000-(E136-Config!$B$5),IF(G136="Em andamento",1000-MIN(E136-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L136" s="35">
+        <f>IF(B136="","",IF(I136&lt;&gt;"",1,N(F136)))</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="32" t="n"/>
@@ -8988,6 +9517,10 @@
         <f>IF(OR(B137="",G137="Concluída"),0,IF(G137="Atrasada",3000+MIN(Config!$B$5-E137,60),IF(G137="Vence em breve",2000-(E137-Config!$B$5),IF(G137="Em andamento",1000-MIN(E137-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L137" s="35">
+        <f>IF(B137="","",IF(I137&lt;&gt;"",1,N(F137)))</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="32" t="n"/>
@@ -9010,6 +9543,10 @@
         <f>IF(OR(B138="",G138="Concluída"),0,IF(G138="Atrasada",3000+MIN(Config!$B$5-E138,60),IF(G138="Vence em breve",2000-(E138-Config!$B$5),IF(G138="Em andamento",1000-MIN(E138-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L138" s="35">
+        <f>IF(B138="","",IF(I138&lt;&gt;"",1,N(F138)))</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="32" t="n"/>
@@ -9032,6 +9569,10 @@
         <f>IF(OR(B139="",G139="Concluída"),0,IF(G139="Atrasada",3000+MIN(Config!$B$5-E139,60),IF(G139="Vence em breve",2000-(E139-Config!$B$5),IF(G139="Em andamento",1000-MIN(E139-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L139" s="35">
+        <f>IF(B139="","",IF(I139&lt;&gt;"",1,N(F139)))</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="32" t="n"/>
@@ -9054,6 +9595,10 @@
         <f>IF(OR(B140="",G140="Concluída"),0,IF(G140="Atrasada",3000+MIN(Config!$B$5-E140,60),IF(G140="Vence em breve",2000-(E140-Config!$B$5),IF(G140="Em andamento",1000-MIN(E140-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L140" s="35">
+        <f>IF(B140="","",IF(I140&lt;&gt;"",1,N(F140)))</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="32" t="n"/>
@@ -9076,6 +9621,10 @@
         <f>IF(OR(B141="",G141="Concluída"),0,IF(G141="Atrasada",3000+MIN(Config!$B$5-E141,60),IF(G141="Vence em breve",2000-(E141-Config!$B$5),IF(G141="Em andamento",1000-MIN(E141-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L141" s="35">
+        <f>IF(B141="","",IF(I141&lt;&gt;"",1,N(F141)))</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="32" t="n"/>
@@ -9098,6 +9647,10 @@
         <f>IF(OR(B142="",G142="Concluída"),0,IF(G142="Atrasada",3000+MIN(Config!$B$5-E142,60),IF(G142="Vence em breve",2000-(E142-Config!$B$5),IF(G142="Em andamento",1000-MIN(E142-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L142" s="35">
+        <f>IF(B142="","",IF(I142&lt;&gt;"",1,N(F142)))</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="32" t="n"/>
@@ -9120,6 +9673,10 @@
         <f>IF(OR(B143="",G143="Concluída"),0,IF(G143="Atrasada",3000+MIN(Config!$B$5-E143,60),IF(G143="Vence em breve",2000-(E143-Config!$B$5),IF(G143="Em andamento",1000-MIN(E143-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L143" s="35">
+        <f>IF(B143="","",IF(I143&lt;&gt;"",1,N(F143)))</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="32" t="n"/>
@@ -9142,6 +9699,10 @@
         <f>IF(OR(B144="",G144="Concluída"),0,IF(G144="Atrasada",3000+MIN(Config!$B$5-E144,60),IF(G144="Vence em breve",2000-(E144-Config!$B$5),IF(G144="Em andamento",1000-MIN(E144-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L144" s="35">
+        <f>IF(B144="","",IF(I144&lt;&gt;"",1,N(F144)))</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="32" t="n"/>
@@ -9164,6 +9725,10 @@
         <f>IF(OR(B145="",G145="Concluída"),0,IF(G145="Atrasada",3000+MIN(Config!$B$5-E145,60),IF(G145="Vence em breve",2000-(E145-Config!$B$5),IF(G145="Em andamento",1000-MIN(E145-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L145" s="35">
+        <f>IF(B145="","",IF(I145&lt;&gt;"",1,N(F145)))</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="32" t="n"/>
@@ -9186,6 +9751,10 @@
         <f>IF(OR(B146="",G146="Concluída"),0,IF(G146="Atrasada",3000+MIN(Config!$B$5-E146,60),IF(G146="Vence em breve",2000-(E146-Config!$B$5),IF(G146="Em andamento",1000-MIN(E146-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L146" s="35">
+        <f>IF(B146="","",IF(I146&lt;&gt;"",1,N(F146)))</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="32" t="n"/>
@@ -9208,6 +9777,10 @@
         <f>IF(OR(B147="",G147="Concluída"),0,IF(G147="Atrasada",3000+MIN(Config!$B$5-E147,60),IF(G147="Vence em breve",2000-(E147-Config!$B$5),IF(G147="Em andamento",1000-MIN(E147-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L147" s="35">
+        <f>IF(B147="","",IF(I147&lt;&gt;"",1,N(F147)))</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="32" t="n"/>
@@ -9230,6 +9803,10 @@
         <f>IF(OR(B148="",G148="Concluída"),0,IF(G148="Atrasada",3000+MIN(Config!$B$5-E148,60),IF(G148="Vence em breve",2000-(E148-Config!$B$5),IF(G148="Em andamento",1000-MIN(E148-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L148" s="35">
+        <f>IF(B148="","",IF(I148&lt;&gt;"",1,N(F148)))</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="32" t="n"/>
@@ -9252,6 +9829,10 @@
         <f>IF(OR(B149="",G149="Concluída"),0,IF(G149="Atrasada",3000+MIN(Config!$B$5-E149,60),IF(G149="Vence em breve",2000-(E149-Config!$B$5),IF(G149="Em andamento",1000-MIN(E149-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L149" s="35">
+        <f>IF(B149="","",IF(I149&lt;&gt;"",1,N(F149)))</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="32" t="n"/>
@@ -9274,6 +9855,10 @@
         <f>IF(OR(B150="",G150="Concluída"),0,IF(G150="Atrasada",3000+MIN(Config!$B$5-E150,60),IF(G150="Vence em breve",2000-(E150-Config!$B$5),IF(G150="Em andamento",1000-MIN(E150-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L150" s="35">
+        <f>IF(B150="","",IF(I150&lt;&gt;"",1,N(F150)))</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="32" t="n"/>
@@ -9296,6 +9881,10 @@
         <f>IF(OR(B151="",G151="Concluída"),0,IF(G151="Atrasada",3000+MIN(Config!$B$5-E151,60),IF(G151="Vence em breve",2000-(E151-Config!$B$5),IF(G151="Em andamento",1000-MIN(E151-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L151" s="35">
+        <f>IF(B151="","",IF(I151&lt;&gt;"",1,N(F151)))</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="32" t="n"/>
@@ -9318,6 +9907,10 @@
         <f>IF(OR(B152="",G152="Concluída"),0,IF(G152="Atrasada",3000+MIN(Config!$B$5-E152,60),IF(G152="Vence em breve",2000-(E152-Config!$B$5),IF(G152="Em andamento",1000-MIN(E152-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L152" s="35">
+        <f>IF(B152="","",IF(I152&lt;&gt;"",1,N(F152)))</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="32" t="n"/>
@@ -9340,6 +9933,10 @@
         <f>IF(OR(B153="",G153="Concluída"),0,IF(G153="Atrasada",3000+MIN(Config!$B$5-E153,60),IF(G153="Vence em breve",2000-(E153-Config!$B$5),IF(G153="Em andamento",1000-MIN(E153-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L153" s="35">
+        <f>IF(B153="","",IF(I153&lt;&gt;"",1,N(F153)))</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="32" t="n"/>
@@ -9362,6 +9959,10 @@
         <f>IF(OR(B154="",G154="Concluída"),0,IF(G154="Atrasada",3000+MIN(Config!$B$5-E154,60),IF(G154="Vence em breve",2000-(E154-Config!$B$5),IF(G154="Em andamento",1000-MIN(E154-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L154" s="35">
+        <f>IF(B154="","",IF(I154&lt;&gt;"",1,N(F154)))</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="32" t="n"/>
@@ -9384,6 +9985,10 @@
         <f>IF(OR(B155="",G155="Concluída"),0,IF(G155="Atrasada",3000+MIN(Config!$B$5-E155,60),IF(G155="Vence em breve",2000-(E155-Config!$B$5),IF(G155="Em andamento",1000-MIN(E155-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L155" s="35">
+        <f>IF(B155="","",IF(I155&lt;&gt;"",1,N(F155)))</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="32" t="n"/>
@@ -9406,6 +10011,10 @@
         <f>IF(OR(B156="",G156="Concluída"),0,IF(G156="Atrasada",3000+MIN(Config!$B$5-E156,60),IF(G156="Vence em breve",2000-(E156-Config!$B$5),IF(G156="Em andamento",1000-MIN(E156-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L156" s="35">
+        <f>IF(B156="","",IF(I156&lt;&gt;"",1,N(F156)))</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="32" t="n"/>
@@ -9428,6 +10037,10 @@
         <f>IF(OR(B157="",G157="Concluída"),0,IF(G157="Atrasada",3000+MIN(Config!$B$5-E157,60),IF(G157="Vence em breve",2000-(E157-Config!$B$5),IF(G157="Em andamento",1000-MIN(E157-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L157" s="35">
+        <f>IF(B157="","",IF(I157&lt;&gt;"",1,N(F157)))</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="32" t="n"/>
@@ -9450,6 +10063,10 @@
         <f>IF(OR(B158="",G158="Concluída"),0,IF(G158="Atrasada",3000+MIN(Config!$B$5-E158,60),IF(G158="Vence em breve",2000-(E158-Config!$B$5),IF(G158="Em andamento",1000-MIN(E158-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L158" s="35">
+        <f>IF(B158="","",IF(I158&lt;&gt;"",1,N(F158)))</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="32" t="n"/>
@@ -9472,6 +10089,10 @@
         <f>IF(OR(B159="",G159="Concluída"),0,IF(G159="Atrasada",3000+MIN(Config!$B$5-E159,60),IF(G159="Vence em breve",2000-(E159-Config!$B$5),IF(G159="Em andamento",1000-MIN(E159-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L159" s="35">
+        <f>IF(B159="","",IF(I159&lt;&gt;"",1,N(F159)))</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="32" t="n"/>
@@ -9494,6 +10115,10 @@
         <f>IF(OR(B160="",G160="Concluída"),0,IF(G160="Atrasada",3000+MIN(Config!$B$5-E160,60),IF(G160="Vence em breve",2000-(E160-Config!$B$5),IF(G160="Em andamento",1000-MIN(E160-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L160" s="35">
+        <f>IF(B160="","",IF(I160&lt;&gt;"",1,N(F160)))</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="32" t="n"/>
@@ -9516,6 +10141,10 @@
         <f>IF(OR(B161="",G161="Concluída"),0,IF(G161="Atrasada",3000+MIN(Config!$B$5-E161,60),IF(G161="Vence em breve",2000-(E161-Config!$B$5),IF(G161="Em andamento",1000-MIN(E161-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L161" s="35">
+        <f>IF(B161="","",IF(I161&lt;&gt;"",1,N(F161)))</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="32" t="n"/>
@@ -9538,6 +10167,10 @@
         <f>IF(OR(B162="",G162="Concluída"),0,IF(G162="Atrasada",3000+MIN(Config!$B$5-E162,60),IF(G162="Vence em breve",2000-(E162-Config!$B$5),IF(G162="Em andamento",1000-MIN(E162-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L162" s="35">
+        <f>IF(B162="","",IF(I162&lt;&gt;"",1,N(F162)))</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="32" t="n"/>
@@ -9560,6 +10193,10 @@
         <f>IF(OR(B163="",G163="Concluída"),0,IF(G163="Atrasada",3000+MIN(Config!$B$5-E163,60),IF(G163="Vence em breve",2000-(E163-Config!$B$5),IF(G163="Em andamento",1000-MIN(E163-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L163" s="35">
+        <f>IF(B163="","",IF(I163&lt;&gt;"",1,N(F163)))</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="32" t="n"/>
@@ -9582,6 +10219,10 @@
         <f>IF(OR(B164="",G164="Concluída"),0,IF(G164="Atrasada",3000+MIN(Config!$B$5-E164,60),IF(G164="Vence em breve",2000-(E164-Config!$B$5),IF(G164="Em andamento",1000-MIN(E164-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L164" s="35">
+        <f>IF(B164="","",IF(I164&lt;&gt;"",1,N(F164)))</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="32" t="n"/>
@@ -9604,6 +10245,10 @@
         <f>IF(OR(B165="",G165="Concluída"),0,IF(G165="Atrasada",3000+MIN(Config!$B$5-E165,60),IF(G165="Vence em breve",2000-(E165-Config!$B$5),IF(G165="Em andamento",1000-MIN(E165-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L165" s="35">
+        <f>IF(B165="","",IF(I165&lt;&gt;"",1,N(F165)))</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="32" t="n"/>
@@ -9626,6 +10271,10 @@
         <f>IF(OR(B166="",G166="Concluída"),0,IF(G166="Atrasada",3000+MIN(Config!$B$5-E166,60),IF(G166="Vence em breve",2000-(E166-Config!$B$5),IF(G166="Em andamento",1000-MIN(E166-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L166" s="35">
+        <f>IF(B166="","",IF(I166&lt;&gt;"",1,N(F166)))</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="32" t="n"/>
@@ -9648,6 +10297,10 @@
         <f>IF(OR(B167="",G167="Concluída"),0,IF(G167="Atrasada",3000+MIN(Config!$B$5-E167,60),IF(G167="Vence em breve",2000-(E167-Config!$B$5),IF(G167="Em andamento",1000-MIN(E167-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L167" s="35">
+        <f>IF(B167="","",IF(I167&lt;&gt;"",1,N(F167)))</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="32" t="n"/>
@@ -9670,6 +10323,10 @@
         <f>IF(OR(B168="",G168="Concluída"),0,IF(G168="Atrasada",3000+MIN(Config!$B$5-E168,60),IF(G168="Vence em breve",2000-(E168-Config!$B$5),IF(G168="Em andamento",1000-MIN(E168-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L168" s="35">
+        <f>IF(B168="","",IF(I168&lt;&gt;"",1,N(F168)))</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="32" t="n"/>
@@ -9692,6 +10349,10 @@
         <f>IF(OR(B169="",G169="Concluída"),0,IF(G169="Atrasada",3000+MIN(Config!$B$5-E169,60),IF(G169="Vence em breve",2000-(E169-Config!$B$5),IF(G169="Em andamento",1000-MIN(E169-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L169" s="35">
+        <f>IF(B169="","",IF(I169&lt;&gt;"",1,N(F169)))</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="32" t="n"/>
@@ -9714,6 +10375,10 @@
         <f>IF(OR(B170="",G170="Concluída"),0,IF(G170="Atrasada",3000+MIN(Config!$B$5-E170,60),IF(G170="Vence em breve",2000-(E170-Config!$B$5),IF(G170="Em andamento",1000-MIN(E170-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L170" s="35">
+        <f>IF(B170="","",IF(I170&lt;&gt;"",1,N(F170)))</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="32" t="n"/>
@@ -9736,6 +10401,10 @@
         <f>IF(OR(B171="",G171="Concluída"),0,IF(G171="Atrasada",3000+MIN(Config!$B$5-E171,60),IF(G171="Vence em breve",2000-(E171-Config!$B$5),IF(G171="Em andamento",1000-MIN(E171-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L171" s="35">
+        <f>IF(B171="","",IF(I171&lt;&gt;"",1,N(F171)))</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="32" t="n"/>
@@ -9758,6 +10427,10 @@
         <f>IF(OR(B172="",G172="Concluída"),0,IF(G172="Atrasada",3000+MIN(Config!$B$5-E172,60),IF(G172="Vence em breve",2000-(E172-Config!$B$5),IF(G172="Em andamento",1000-MIN(E172-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L172" s="35">
+        <f>IF(B172="","",IF(I172&lt;&gt;"",1,N(F172)))</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="32" t="n"/>
@@ -9780,6 +10453,10 @@
         <f>IF(OR(B173="",G173="Concluída"),0,IF(G173="Atrasada",3000+MIN(Config!$B$5-E173,60),IF(G173="Vence em breve",2000-(E173-Config!$B$5),IF(G173="Em andamento",1000-MIN(E173-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L173" s="35">
+        <f>IF(B173="","",IF(I173&lt;&gt;"",1,N(F173)))</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="32" t="n"/>
@@ -9802,6 +10479,10 @@
         <f>IF(OR(B174="",G174="Concluída"),0,IF(G174="Atrasada",3000+MIN(Config!$B$5-E174,60),IF(G174="Vence em breve",2000-(E174-Config!$B$5),IF(G174="Em andamento",1000-MIN(E174-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L174" s="35">
+        <f>IF(B174="","",IF(I174&lt;&gt;"",1,N(F174)))</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="32" t="n"/>
@@ -9824,6 +10505,10 @@
         <f>IF(OR(B175="",G175="Concluída"),0,IF(G175="Atrasada",3000+MIN(Config!$B$5-E175,60),IF(G175="Vence em breve",2000-(E175-Config!$B$5),IF(G175="Em andamento",1000-MIN(E175-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L175" s="35">
+        <f>IF(B175="","",IF(I175&lt;&gt;"",1,N(F175)))</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="32" t="n"/>
@@ -9846,6 +10531,10 @@
         <f>IF(OR(B176="",G176="Concluída"),0,IF(G176="Atrasada",3000+MIN(Config!$B$5-E176,60),IF(G176="Vence em breve",2000-(E176-Config!$B$5),IF(G176="Em andamento",1000-MIN(E176-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L176" s="35">
+        <f>IF(B176="","",IF(I176&lt;&gt;"",1,N(F176)))</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="32" t="n"/>
@@ -9868,6 +10557,10 @@
         <f>IF(OR(B177="",G177="Concluída"),0,IF(G177="Atrasada",3000+MIN(Config!$B$5-E177,60),IF(G177="Vence em breve",2000-(E177-Config!$B$5),IF(G177="Em andamento",1000-MIN(E177-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L177" s="35">
+        <f>IF(B177="","",IF(I177&lt;&gt;"",1,N(F177)))</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="32" t="n"/>
@@ -9890,6 +10583,10 @@
         <f>IF(OR(B178="",G178="Concluída"),0,IF(G178="Atrasada",3000+MIN(Config!$B$5-E178,60),IF(G178="Vence em breve",2000-(E178-Config!$B$5),IF(G178="Em andamento",1000-MIN(E178-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L178" s="35">
+        <f>IF(B178="","",IF(I178&lt;&gt;"",1,N(F178)))</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="32" t="n"/>
@@ -9912,6 +10609,10 @@
         <f>IF(OR(B179="",G179="Concluída"),0,IF(G179="Atrasada",3000+MIN(Config!$B$5-E179,60),IF(G179="Vence em breve",2000-(E179-Config!$B$5),IF(G179="Em andamento",1000-MIN(E179-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L179" s="35">
+        <f>IF(B179="","",IF(I179&lt;&gt;"",1,N(F179)))</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="32" t="n"/>
@@ -9934,6 +10635,10 @@
         <f>IF(OR(B180="",G180="Concluída"),0,IF(G180="Atrasada",3000+MIN(Config!$B$5-E180,60),IF(G180="Vence em breve",2000-(E180-Config!$B$5),IF(G180="Em andamento",1000-MIN(E180-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L180" s="35">
+        <f>IF(B180="","",IF(I180&lt;&gt;"",1,N(F180)))</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="32" t="n"/>
@@ -9956,6 +10661,10 @@
         <f>IF(OR(B181="",G181="Concluída"),0,IF(G181="Atrasada",3000+MIN(Config!$B$5-E181,60),IF(G181="Vence em breve",2000-(E181-Config!$B$5),IF(G181="Em andamento",1000-MIN(E181-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L181" s="35">
+        <f>IF(B181="","",IF(I181&lt;&gt;"",1,N(F181)))</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="32" t="n"/>
@@ -9978,6 +10687,10 @@
         <f>IF(OR(B182="",G182="Concluída"),0,IF(G182="Atrasada",3000+MIN(Config!$B$5-E182,60),IF(G182="Vence em breve",2000-(E182-Config!$B$5),IF(G182="Em andamento",1000-MIN(E182-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L182" s="35">
+        <f>IF(B182="","",IF(I182&lt;&gt;"",1,N(F182)))</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="32" t="n"/>
@@ -10000,6 +10713,10 @@
         <f>IF(OR(B183="",G183="Concluída"),0,IF(G183="Atrasada",3000+MIN(Config!$B$5-E183,60),IF(G183="Vence em breve",2000-(E183-Config!$B$5),IF(G183="Em andamento",1000-MIN(E183-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L183" s="35">
+        <f>IF(B183="","",IF(I183&lt;&gt;"",1,N(F183)))</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="32" t="n"/>
@@ -10022,6 +10739,10 @@
         <f>IF(OR(B184="",G184="Concluída"),0,IF(G184="Atrasada",3000+MIN(Config!$B$5-E184,60),IF(G184="Vence em breve",2000-(E184-Config!$B$5),IF(G184="Em andamento",1000-MIN(E184-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L184" s="35">
+        <f>IF(B184="","",IF(I184&lt;&gt;"",1,N(F184)))</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="32" t="n"/>
@@ -10044,6 +10765,10 @@
         <f>IF(OR(B185="",G185="Concluída"),0,IF(G185="Atrasada",3000+MIN(Config!$B$5-E185,60),IF(G185="Vence em breve",2000-(E185-Config!$B$5),IF(G185="Em andamento",1000-MIN(E185-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L185" s="35">
+        <f>IF(B185="","",IF(I185&lt;&gt;"",1,N(F185)))</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="32" t="n"/>
@@ -10066,6 +10791,10 @@
         <f>IF(OR(B186="",G186="Concluída"),0,IF(G186="Atrasada",3000+MIN(Config!$B$5-E186,60),IF(G186="Vence em breve",2000-(E186-Config!$B$5),IF(G186="Em andamento",1000-MIN(E186-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L186" s="35">
+        <f>IF(B186="","",IF(I186&lt;&gt;"",1,N(F186)))</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="32" t="n"/>
@@ -10088,6 +10817,10 @@
         <f>IF(OR(B187="",G187="Concluída"),0,IF(G187="Atrasada",3000+MIN(Config!$B$5-E187,60),IF(G187="Vence em breve",2000-(E187-Config!$B$5),IF(G187="Em andamento",1000-MIN(E187-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L187" s="35">
+        <f>IF(B187="","",IF(I187&lt;&gt;"",1,N(F187)))</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="32" t="n"/>
@@ -10110,6 +10843,10 @@
         <f>IF(OR(B188="",G188="Concluída"),0,IF(G188="Atrasada",3000+MIN(Config!$B$5-E188,60),IF(G188="Vence em breve",2000-(E188-Config!$B$5),IF(G188="Em andamento",1000-MIN(E188-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L188" s="35">
+        <f>IF(B188="","",IF(I188&lt;&gt;"",1,N(F188)))</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="32" t="n"/>
@@ -10132,6 +10869,10 @@
         <f>IF(OR(B189="",G189="Concluída"),0,IF(G189="Atrasada",3000+MIN(Config!$B$5-E189,60),IF(G189="Vence em breve",2000-(E189-Config!$B$5),IF(G189="Em andamento",1000-MIN(E189-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L189" s="35">
+        <f>IF(B189="","",IF(I189&lt;&gt;"",1,N(F189)))</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="32" t="n"/>
@@ -10154,6 +10895,10 @@
         <f>IF(OR(B190="",G190="Concluída"),0,IF(G190="Atrasada",3000+MIN(Config!$B$5-E190,60),IF(G190="Vence em breve",2000-(E190-Config!$B$5),IF(G190="Em andamento",1000-MIN(E190-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L190" s="35">
+        <f>IF(B190="","",IF(I190&lt;&gt;"",1,N(F190)))</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="32" t="n"/>
@@ -10176,6 +10921,10 @@
         <f>IF(OR(B191="",G191="Concluída"),0,IF(G191="Atrasada",3000+MIN(Config!$B$5-E191,60),IF(G191="Vence em breve",2000-(E191-Config!$B$5),IF(G191="Em andamento",1000-MIN(E191-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L191" s="35">
+        <f>IF(B191="","",IF(I191&lt;&gt;"",1,N(F191)))</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="32" t="n"/>
@@ -10198,6 +10947,10 @@
         <f>IF(OR(B192="",G192="Concluída"),0,IF(G192="Atrasada",3000+MIN(Config!$B$5-E192,60),IF(G192="Vence em breve",2000-(E192-Config!$B$5),IF(G192="Em andamento",1000-MIN(E192-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L192" s="35">
+        <f>IF(B192="","",IF(I192&lt;&gt;"",1,N(F192)))</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="32" t="n"/>
@@ -10220,6 +10973,10 @@
         <f>IF(OR(B193="",G193="Concluída"),0,IF(G193="Atrasada",3000+MIN(Config!$B$5-E193,60),IF(G193="Vence em breve",2000-(E193-Config!$B$5),IF(G193="Em andamento",1000-MIN(E193-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L193" s="35">
+        <f>IF(B193="","",IF(I193&lt;&gt;"",1,N(F193)))</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="32" t="n"/>
@@ -10242,6 +10999,10 @@
         <f>IF(OR(B194="",G194="Concluída"),0,IF(G194="Atrasada",3000+MIN(Config!$B$5-E194,60),IF(G194="Vence em breve",2000-(E194-Config!$B$5),IF(G194="Em andamento",1000-MIN(E194-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L194" s="35">
+        <f>IF(B194="","",IF(I194&lt;&gt;"",1,N(F194)))</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="32" t="n"/>
@@ -10264,6 +11025,10 @@
         <f>IF(OR(B195="",G195="Concluída"),0,IF(G195="Atrasada",3000+MIN(Config!$B$5-E195,60),IF(G195="Vence em breve",2000-(E195-Config!$B$5),IF(G195="Em andamento",1000-MIN(E195-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L195" s="35">
+        <f>IF(B195="","",IF(I195&lt;&gt;"",1,N(F195)))</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="32" t="n"/>
@@ -10286,6 +11051,10 @@
         <f>IF(OR(B196="",G196="Concluída"),0,IF(G196="Atrasada",3000+MIN(Config!$B$5-E196,60),IF(G196="Vence em breve",2000-(E196-Config!$B$5),IF(G196="Em andamento",1000-MIN(E196-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L196" s="35">
+        <f>IF(B196="","",IF(I196&lt;&gt;"",1,N(F196)))</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="32" t="n"/>
@@ -10308,6 +11077,10 @@
         <f>IF(OR(B197="",G197="Concluída"),0,IF(G197="Atrasada",3000+MIN(Config!$B$5-E197,60),IF(G197="Vence em breve",2000-(E197-Config!$B$5),IF(G197="Em andamento",1000-MIN(E197-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L197" s="35">
+        <f>IF(B197="","",IF(I197&lt;&gt;"",1,N(F197)))</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="32" t="n"/>
@@ -10330,6 +11103,10 @@
         <f>IF(OR(B198="",G198="Concluída"),0,IF(G198="Atrasada",3000+MIN(Config!$B$5-E198,60),IF(G198="Vence em breve",2000-(E198-Config!$B$5),IF(G198="Em andamento",1000-MIN(E198-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L198" s="35">
+        <f>IF(B198="","",IF(I198&lt;&gt;"",1,N(F198)))</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="32" t="n"/>
@@ -10352,6 +11129,10 @@
         <f>IF(OR(B199="",G199="Concluída"),0,IF(G199="Atrasada",3000+MIN(Config!$B$5-E199,60),IF(G199="Vence em breve",2000-(E199-Config!$B$5),IF(G199="Em andamento",1000-MIN(E199-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L199" s="35">
+        <f>IF(B199="","",IF(I199&lt;&gt;"",1,N(F199)))</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="32" t="n"/>
@@ -10374,6 +11155,10 @@
         <f>IF(OR(B200="",G200="Concluída"),0,IF(G200="Atrasada",3000+MIN(Config!$B$5-E200,60),IF(G200="Vence em breve",2000-(E200-Config!$B$5),IF(G200="Em andamento",1000-MIN(E200-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L200" s="35">
+        <f>IF(B200="","",IF(I200&lt;&gt;"",1,N(F200)))</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="32" t="n"/>
@@ -10396,6 +11181,10 @@
         <f>IF(OR(B201="",G201="Concluída"),0,IF(G201="Atrasada",3000+MIN(Config!$B$5-E201,60),IF(G201="Vence em breve",2000-(E201-Config!$B$5),IF(G201="Em andamento",1000-MIN(E201-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L201" s="35">
+        <f>IF(B201="","",IF(I201&lt;&gt;"",1,N(F201)))</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="32" t="n"/>
@@ -10418,6 +11207,10 @@
         <f>IF(OR(B202="",G202="Concluída"),0,IF(G202="Atrasada",3000+MIN(Config!$B$5-E202,60),IF(G202="Vence em breve",2000-(E202-Config!$B$5),IF(G202="Em andamento",1000-MIN(E202-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L202" s="35">
+        <f>IF(B202="","",IF(I202&lt;&gt;"",1,N(F202)))</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="32" t="n"/>
@@ -10440,6 +11233,10 @@
         <f>IF(OR(B203="",G203="Concluída"),0,IF(G203="Atrasada",3000+MIN(Config!$B$5-E203,60),IF(G203="Vence em breve",2000-(E203-Config!$B$5),IF(G203="Em andamento",1000-MIN(E203-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L203" s="35">
+        <f>IF(B203="","",IF(I203&lt;&gt;"",1,N(F203)))</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="32" t="n"/>
@@ -10462,6 +11259,10 @@
         <f>IF(OR(B204="",G204="Concluída"),0,IF(G204="Atrasada",3000+MIN(Config!$B$5-E204,60),IF(G204="Vence em breve",2000-(E204-Config!$B$5),IF(G204="Em andamento",1000-MIN(E204-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L204" s="35">
+        <f>IF(B204="","",IF(I204&lt;&gt;"",1,N(F204)))</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="32" t="n"/>
@@ -10484,6 +11285,10 @@
         <f>IF(OR(B205="",G205="Concluída"),0,IF(G205="Atrasada",3000+MIN(Config!$B$5-E205,60),IF(G205="Vence em breve",2000-(E205-Config!$B$5),IF(G205="Em andamento",1000-MIN(E205-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L205" s="35">
+        <f>IF(B205="","",IF(I205&lt;&gt;"",1,N(F205)))</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="32" t="n"/>
@@ -10506,6 +11311,10 @@
         <f>IF(OR(B206="",G206="Concluída"),0,IF(G206="Atrasada",3000+MIN(Config!$B$5-E206,60),IF(G206="Vence em breve",2000-(E206-Config!$B$5),IF(G206="Em andamento",1000-MIN(E206-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L206" s="35">
+        <f>IF(B206="","",IF(I206&lt;&gt;"",1,N(F206)))</f>
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="32" t="n"/>
@@ -10528,6 +11337,10 @@
         <f>IF(OR(B207="",G207="Concluída"),0,IF(G207="Atrasada",3000+MIN(Config!$B$5-E207,60),IF(G207="Vence em breve",2000-(E207-Config!$B$5),IF(G207="Em andamento",1000-MIN(E207-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L207" s="35">
+        <f>IF(B207="","",IF(I207&lt;&gt;"",1,N(F207)))</f>
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="32" t="n"/>
@@ -10550,6 +11363,10 @@
         <f>IF(OR(B208="",G208="Concluída"),0,IF(G208="Atrasada",3000+MIN(Config!$B$5-E208,60),IF(G208="Vence em breve",2000-(E208-Config!$B$5),IF(G208="Em andamento",1000-MIN(E208-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L208" s="35">
+        <f>IF(B208="","",IF(I208&lt;&gt;"",1,N(F208)))</f>
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="32" t="n"/>
@@ -10572,6 +11389,10 @@
         <f>IF(OR(B209="",G209="Concluída"),0,IF(G209="Atrasada",3000+MIN(Config!$B$5-E209,60),IF(G209="Vence em breve",2000-(E209-Config!$B$5),IF(G209="Em andamento",1000-MIN(E209-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L209" s="35">
+        <f>IF(B209="","",IF(I209&lt;&gt;"",1,N(F209)))</f>
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="32" t="n"/>
@@ -10594,6 +11415,10 @@
         <f>IF(OR(B210="",G210="Concluída"),0,IF(G210="Atrasada",3000+MIN(Config!$B$5-E210,60),IF(G210="Vence em breve",2000-(E210-Config!$B$5),IF(G210="Em andamento",1000-MIN(E210-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L210" s="35">
+        <f>IF(B210="","",IF(I210&lt;&gt;"",1,N(F210)))</f>
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="32" t="n"/>
@@ -10616,6 +11441,10 @@
         <f>IF(OR(B211="",G211="Concluída"),0,IF(G211="Atrasada",3000+MIN(Config!$B$5-E211,60),IF(G211="Vence em breve",2000-(E211-Config!$B$5),IF(G211="Em andamento",1000-MIN(E211-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L211" s="35">
+        <f>IF(B211="","",IF(I211&lt;&gt;"",1,N(F211)))</f>
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="32" t="n"/>
@@ -10638,6 +11467,10 @@
         <f>IF(OR(B212="",G212="Concluída"),0,IF(G212="Atrasada",3000+MIN(Config!$B$5-E212,60),IF(G212="Vence em breve",2000-(E212-Config!$B$5),IF(G212="Em andamento",1000-MIN(E212-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L212" s="35">
+        <f>IF(B212="","",IF(I212&lt;&gt;"",1,N(F212)))</f>
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="32" t="n"/>
@@ -10660,6 +11493,10 @@
         <f>IF(OR(B213="",G213="Concluída"),0,IF(G213="Atrasada",3000+MIN(Config!$B$5-E213,60),IF(G213="Vence em breve",2000-(E213-Config!$B$5),IF(G213="Em andamento",1000-MIN(E213-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L213" s="35">
+        <f>IF(B213="","",IF(I213&lt;&gt;"",1,N(F213)))</f>
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="32" t="n"/>
@@ -10682,6 +11519,10 @@
         <f>IF(OR(B214="",G214="Concluída"),0,IF(G214="Atrasada",3000+MIN(Config!$B$5-E214,60),IF(G214="Vence em breve",2000-(E214-Config!$B$5),IF(G214="Em andamento",1000-MIN(E214-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L214" s="35">
+        <f>IF(B214="","",IF(I214&lt;&gt;"",1,N(F214)))</f>
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="32" t="n"/>
@@ -10704,6 +11545,10 @@
         <f>IF(OR(B215="",G215="Concluída"),0,IF(G215="Atrasada",3000+MIN(Config!$B$5-E215,60),IF(G215="Vence em breve",2000-(E215-Config!$B$5),IF(G215="Em andamento",1000-MIN(E215-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L215" s="35">
+        <f>IF(B215="","",IF(I215&lt;&gt;"",1,N(F215)))</f>
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="32" t="n"/>
@@ -10726,6 +11571,10 @@
         <f>IF(OR(B216="",G216="Concluída"),0,IF(G216="Atrasada",3000+MIN(Config!$B$5-E216,60),IF(G216="Vence em breve",2000-(E216-Config!$B$5),IF(G216="Em andamento",1000-MIN(E216-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L216" s="35">
+        <f>IF(B216="","",IF(I216&lt;&gt;"",1,N(F216)))</f>
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="32" t="n"/>
@@ -10748,6 +11597,10 @@
         <f>IF(OR(B217="",G217="Concluída"),0,IF(G217="Atrasada",3000+MIN(Config!$B$5-E217,60),IF(G217="Vence em breve",2000-(E217-Config!$B$5),IF(G217="Em andamento",1000-MIN(E217-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L217" s="35">
+        <f>IF(B217="","",IF(I217&lt;&gt;"",1,N(F217)))</f>
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="32" t="n"/>
@@ -10770,6 +11623,10 @@
         <f>IF(OR(B218="",G218="Concluída"),0,IF(G218="Atrasada",3000+MIN(Config!$B$5-E218,60),IF(G218="Vence em breve",2000-(E218-Config!$B$5),IF(G218="Em andamento",1000-MIN(E218-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L218" s="35">
+        <f>IF(B218="","",IF(I218&lt;&gt;"",1,N(F218)))</f>
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="32" t="n"/>
@@ -10792,6 +11649,10 @@
         <f>IF(OR(B219="",G219="Concluída"),0,IF(G219="Atrasada",3000+MIN(Config!$B$5-E219,60),IF(G219="Vence em breve",2000-(E219-Config!$B$5),IF(G219="Em andamento",1000-MIN(E219-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L219" s="35">
+        <f>IF(B219="","",IF(I219&lt;&gt;"",1,N(F219)))</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="32" t="n"/>
@@ -10814,6 +11675,10 @@
         <f>IF(OR(B220="",G220="Concluída"),0,IF(G220="Atrasada",3000+MIN(Config!$B$5-E220,60),IF(G220="Vence em breve",2000-(E220-Config!$B$5),IF(G220="Em andamento",1000-MIN(E220-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L220" s="35">
+        <f>IF(B220="","",IF(I220&lt;&gt;"",1,N(F220)))</f>
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="32" t="n"/>
@@ -10836,6 +11701,10 @@
         <f>IF(OR(B221="",G221="Concluída"),0,IF(G221="Atrasada",3000+MIN(Config!$B$5-E221,60),IF(G221="Vence em breve",2000-(E221-Config!$B$5),IF(G221="Em andamento",1000-MIN(E221-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L221" s="35">
+        <f>IF(B221="","",IF(I221&lt;&gt;"",1,N(F221)))</f>
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="32" t="n"/>
@@ -10858,6 +11727,10 @@
         <f>IF(OR(B222="",G222="Concluída"),0,IF(G222="Atrasada",3000+MIN(Config!$B$5-E222,60),IF(G222="Vence em breve",2000-(E222-Config!$B$5),IF(G222="Em andamento",1000-MIN(E222-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L222" s="35">
+        <f>IF(B222="","",IF(I222&lt;&gt;"",1,N(F222)))</f>
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="32" t="n"/>
@@ -10880,6 +11753,10 @@
         <f>IF(OR(B223="",G223="Concluída"),0,IF(G223="Atrasada",3000+MIN(Config!$B$5-E223,60),IF(G223="Vence em breve",2000-(E223-Config!$B$5),IF(G223="Em andamento",1000-MIN(E223-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L223" s="35">
+        <f>IF(B223="","",IF(I223&lt;&gt;"",1,N(F223)))</f>
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="32" t="n"/>
@@ -10902,6 +11779,10 @@
         <f>IF(OR(B224="",G224="Concluída"),0,IF(G224="Atrasada",3000+MIN(Config!$B$5-E224,60),IF(G224="Vence em breve",2000-(E224-Config!$B$5),IF(G224="Em andamento",1000-MIN(E224-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L224" s="35">
+        <f>IF(B224="","",IF(I224&lt;&gt;"",1,N(F224)))</f>
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="32" t="n"/>
@@ -10924,6 +11805,10 @@
         <f>IF(OR(B225="",G225="Concluída"),0,IF(G225="Atrasada",3000+MIN(Config!$B$5-E225,60),IF(G225="Vence em breve",2000-(E225-Config!$B$5),IF(G225="Em andamento",1000-MIN(E225-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L225" s="35">
+        <f>IF(B225="","",IF(I225&lt;&gt;"",1,N(F225)))</f>
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="32" t="n"/>
@@ -10946,6 +11831,10 @@
         <f>IF(OR(B226="",G226="Concluída"),0,IF(G226="Atrasada",3000+MIN(Config!$B$5-E226,60),IF(G226="Vence em breve",2000-(E226-Config!$B$5),IF(G226="Em andamento",1000-MIN(E226-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L226" s="35">
+        <f>IF(B226="","",IF(I226&lt;&gt;"",1,N(F226)))</f>
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="32" t="n"/>
@@ -10968,6 +11857,10 @@
         <f>IF(OR(B227="",G227="Concluída"),0,IF(G227="Atrasada",3000+MIN(Config!$B$5-E227,60),IF(G227="Vence em breve",2000-(E227-Config!$B$5),IF(G227="Em andamento",1000-MIN(E227-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L227" s="35">
+        <f>IF(B227="","",IF(I227&lt;&gt;"",1,N(F227)))</f>
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="32" t="n"/>
@@ -10990,6 +11883,10 @@
         <f>IF(OR(B228="",G228="Concluída"),0,IF(G228="Atrasada",3000+MIN(Config!$B$5-E228,60),IF(G228="Vence em breve",2000-(E228-Config!$B$5),IF(G228="Em andamento",1000-MIN(E228-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L228" s="35">
+        <f>IF(B228="","",IF(I228&lt;&gt;"",1,N(F228)))</f>
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="32" t="n"/>
@@ -11012,6 +11909,10 @@
         <f>IF(OR(B229="",G229="Concluída"),0,IF(G229="Atrasada",3000+MIN(Config!$B$5-E229,60),IF(G229="Vence em breve",2000-(E229-Config!$B$5),IF(G229="Em andamento",1000-MIN(E229-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L229" s="35">
+        <f>IF(B229="","",IF(I229&lt;&gt;"",1,N(F229)))</f>
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="32" t="n"/>
@@ -11034,6 +11935,10 @@
         <f>IF(OR(B230="",G230="Concluída"),0,IF(G230="Atrasada",3000+MIN(Config!$B$5-E230,60),IF(G230="Vence em breve",2000-(E230-Config!$B$5),IF(G230="Em andamento",1000-MIN(E230-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L230" s="35">
+        <f>IF(B230="","",IF(I230&lt;&gt;"",1,N(F230)))</f>
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="32" t="n"/>
@@ -11056,6 +11961,10 @@
         <f>IF(OR(B231="",G231="Concluída"),0,IF(G231="Atrasada",3000+MIN(Config!$B$5-E231,60),IF(G231="Vence em breve",2000-(E231-Config!$B$5),IF(G231="Em andamento",1000-MIN(E231-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L231" s="35">
+        <f>IF(B231="","",IF(I231&lt;&gt;"",1,N(F231)))</f>
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="32" t="n"/>
@@ -11078,6 +11987,10 @@
         <f>IF(OR(B232="",G232="Concluída"),0,IF(G232="Atrasada",3000+MIN(Config!$B$5-E232,60),IF(G232="Vence em breve",2000-(E232-Config!$B$5),IF(G232="Em andamento",1000-MIN(E232-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L232" s="35">
+        <f>IF(B232="","",IF(I232&lt;&gt;"",1,N(F232)))</f>
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="32" t="n"/>
@@ -11100,6 +12013,10 @@
         <f>IF(OR(B233="",G233="Concluída"),0,IF(G233="Atrasada",3000+MIN(Config!$B$5-E233,60),IF(G233="Vence em breve",2000-(E233-Config!$B$5),IF(G233="Em andamento",1000-MIN(E233-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L233" s="35">
+        <f>IF(B233="","",IF(I233&lt;&gt;"",1,N(F233)))</f>
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="32" t="n"/>
@@ -11122,6 +12039,10 @@
         <f>IF(OR(B234="",G234="Concluída"),0,IF(G234="Atrasada",3000+MIN(Config!$B$5-E234,60),IF(G234="Vence em breve",2000-(E234-Config!$B$5),IF(G234="Em andamento",1000-MIN(E234-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L234" s="35">
+        <f>IF(B234="","",IF(I234&lt;&gt;"",1,N(F234)))</f>
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="32" t="n"/>
@@ -11144,6 +12065,10 @@
         <f>IF(OR(B235="",G235="Concluída"),0,IF(G235="Atrasada",3000+MIN(Config!$B$5-E235,60),IF(G235="Vence em breve",2000-(E235-Config!$B$5),IF(G235="Em andamento",1000-MIN(E235-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L235" s="35">
+        <f>IF(B235="","",IF(I235&lt;&gt;"",1,N(F235)))</f>
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="32" t="n"/>
@@ -11166,6 +12091,10 @@
         <f>IF(OR(B236="",G236="Concluída"),0,IF(G236="Atrasada",3000+MIN(Config!$B$5-E236,60),IF(G236="Vence em breve",2000-(E236-Config!$B$5),IF(G236="Em andamento",1000-MIN(E236-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L236" s="35">
+        <f>IF(B236="","",IF(I236&lt;&gt;"",1,N(F236)))</f>
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="32" t="n"/>
@@ -11188,6 +12117,10 @@
         <f>IF(OR(B237="",G237="Concluída"),0,IF(G237="Atrasada",3000+MIN(Config!$B$5-E237,60),IF(G237="Vence em breve",2000-(E237-Config!$B$5),IF(G237="Em andamento",1000-MIN(E237-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L237" s="35">
+        <f>IF(B237="","",IF(I237&lt;&gt;"",1,N(F237)))</f>
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="32" t="n"/>
@@ -11210,6 +12143,10 @@
         <f>IF(OR(B238="",G238="Concluída"),0,IF(G238="Atrasada",3000+MIN(Config!$B$5-E238,60),IF(G238="Vence em breve",2000-(E238-Config!$B$5),IF(G238="Em andamento",1000-MIN(E238-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L238" s="35">
+        <f>IF(B238="","",IF(I238&lt;&gt;"",1,N(F238)))</f>
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="32" t="n"/>
@@ -11232,6 +12169,10 @@
         <f>IF(OR(B239="",G239="Concluída"),0,IF(G239="Atrasada",3000+MIN(Config!$B$5-E239,60),IF(G239="Vence em breve",2000-(E239-Config!$B$5),IF(G239="Em andamento",1000-MIN(E239-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L239" s="35">
+        <f>IF(B239="","",IF(I239&lt;&gt;"",1,N(F239)))</f>
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="32" t="n"/>
@@ -11254,6 +12195,10 @@
         <f>IF(OR(B240="",G240="Concluída"),0,IF(G240="Atrasada",3000+MIN(Config!$B$5-E240,60),IF(G240="Vence em breve",2000-(E240-Config!$B$5),IF(G240="Em andamento",1000-MIN(E240-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L240" s="35">
+        <f>IF(B240="","",IF(I240&lt;&gt;"",1,N(F240)))</f>
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="32" t="n"/>
@@ -11276,6 +12221,10 @@
         <f>IF(OR(B241="",G241="Concluída"),0,IF(G241="Atrasada",3000+MIN(Config!$B$5-E241,60),IF(G241="Vence em breve",2000-(E241-Config!$B$5),IF(G241="Em andamento",1000-MIN(E241-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L241" s="35">
+        <f>IF(B241="","",IF(I241&lt;&gt;"",1,N(F241)))</f>
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="32" t="n"/>
@@ -11298,6 +12247,10 @@
         <f>IF(OR(B242="",G242="Concluída"),0,IF(G242="Atrasada",3000+MIN(Config!$B$5-E242,60),IF(G242="Vence em breve",2000-(E242-Config!$B$5),IF(G242="Em andamento",1000-MIN(E242-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L242" s="35">
+        <f>IF(B242="","",IF(I242&lt;&gt;"",1,N(F242)))</f>
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="32" t="n"/>
@@ -11320,6 +12273,10 @@
         <f>IF(OR(B243="",G243="Concluída"),0,IF(G243="Atrasada",3000+MIN(Config!$B$5-E243,60),IF(G243="Vence em breve",2000-(E243-Config!$B$5),IF(G243="Em andamento",1000-MIN(E243-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L243" s="35">
+        <f>IF(B243="","",IF(I243&lt;&gt;"",1,N(F243)))</f>
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="32" t="n"/>
@@ -11342,6 +12299,10 @@
         <f>IF(OR(B244="",G244="Concluída"),0,IF(G244="Atrasada",3000+MIN(Config!$B$5-E244,60),IF(G244="Vence em breve",2000-(E244-Config!$B$5),IF(G244="Em andamento",1000-MIN(E244-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L244" s="35">
+        <f>IF(B244="","",IF(I244&lt;&gt;"",1,N(F244)))</f>
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="32" t="n"/>
@@ -11364,6 +12325,10 @@
         <f>IF(OR(B245="",G245="Concluída"),0,IF(G245="Atrasada",3000+MIN(Config!$B$5-E245,60),IF(G245="Vence em breve",2000-(E245-Config!$B$5),IF(G245="Em andamento",1000-MIN(E245-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L245" s="35">
+        <f>IF(B245="","",IF(I245&lt;&gt;"",1,N(F245)))</f>
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="32" t="n"/>
@@ -11386,6 +12351,10 @@
         <f>IF(OR(B246="",G246="Concluída"),0,IF(G246="Atrasada",3000+MIN(Config!$B$5-E246,60),IF(G246="Vence em breve",2000-(E246-Config!$B$5),IF(G246="Em andamento",1000-MIN(E246-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L246" s="35">
+        <f>IF(B246="","",IF(I246&lt;&gt;"",1,N(F246)))</f>
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="32" t="n"/>
@@ -11408,6 +12377,10 @@
         <f>IF(OR(B247="",G247="Concluída"),0,IF(G247="Atrasada",3000+MIN(Config!$B$5-E247,60),IF(G247="Vence em breve",2000-(E247-Config!$B$5),IF(G247="Em andamento",1000-MIN(E247-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L247" s="35">
+        <f>IF(B247="","",IF(I247&lt;&gt;"",1,N(F247)))</f>
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="32" t="n"/>
@@ -11430,6 +12403,10 @@
         <f>IF(OR(B248="",G248="Concluída"),0,IF(G248="Atrasada",3000+MIN(Config!$B$5-E248,60),IF(G248="Vence em breve",2000-(E248-Config!$B$5),IF(G248="Em andamento",1000-MIN(E248-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L248" s="35">
+        <f>IF(B248="","",IF(I248&lt;&gt;"",1,N(F248)))</f>
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="32" t="n"/>
@@ -11452,6 +12429,10 @@
         <f>IF(OR(B249="",G249="Concluída"),0,IF(G249="Atrasada",3000+MIN(Config!$B$5-E249,60),IF(G249="Vence em breve",2000-(E249-Config!$B$5),IF(G249="Em andamento",1000-MIN(E249-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L249" s="35">
+        <f>IF(B249="","",IF(I249&lt;&gt;"",1,N(F249)))</f>
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="32" t="n"/>
@@ -11474,6 +12455,10 @@
         <f>IF(OR(B250="",G250="Concluída"),0,IF(G250="Atrasada",3000+MIN(Config!$B$5-E250,60),IF(G250="Vence em breve",2000-(E250-Config!$B$5),IF(G250="Em andamento",1000-MIN(E250-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L250" s="35">
+        <f>IF(B250="","",IF(I250&lt;&gt;"",1,N(F250)))</f>
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="32" t="n"/>
@@ -11496,6 +12481,10 @@
         <f>IF(OR(B251="",G251="Concluída"),0,IF(G251="Atrasada",3000+MIN(Config!$B$5-E251,60),IF(G251="Vence em breve",2000-(E251-Config!$B$5),IF(G251="Em andamento",1000-MIN(E251-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L251" s="35">
+        <f>IF(B251="","",IF(I251&lt;&gt;"",1,N(F251)))</f>
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="32" t="n"/>
@@ -11518,6 +12507,10 @@
         <f>IF(OR(B252="",G252="Concluída"),0,IF(G252="Atrasada",3000+MIN(Config!$B$5-E252,60),IF(G252="Vence em breve",2000-(E252-Config!$B$5),IF(G252="Em andamento",1000-MIN(E252-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L252" s="35">
+        <f>IF(B252="","",IF(I252&lt;&gt;"",1,N(F252)))</f>
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="32" t="n"/>
@@ -11540,6 +12533,10 @@
         <f>IF(OR(B253="",G253="Concluída"),0,IF(G253="Atrasada",3000+MIN(Config!$B$5-E253,60),IF(G253="Vence em breve",2000-(E253-Config!$B$5),IF(G253="Em andamento",1000-MIN(E253-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L253" s="35">
+        <f>IF(B253="","",IF(I253&lt;&gt;"",1,N(F253)))</f>
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="32" t="n"/>
@@ -11562,6 +12559,10 @@
         <f>IF(OR(B254="",G254="Concluída"),0,IF(G254="Atrasada",3000+MIN(Config!$B$5-E254,60),IF(G254="Vence em breve",2000-(E254-Config!$B$5),IF(G254="Em andamento",1000-MIN(E254-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L254" s="35">
+        <f>IF(B254="","",IF(I254&lt;&gt;"",1,N(F254)))</f>
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="32" t="n"/>
@@ -11584,6 +12585,10 @@
         <f>IF(OR(B255="",G255="Concluída"),0,IF(G255="Atrasada",3000+MIN(Config!$B$5-E255,60),IF(G255="Vence em breve",2000-(E255-Config!$B$5),IF(G255="Em andamento",1000-MIN(E255-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L255" s="35">
+        <f>IF(B255="","",IF(I255&lt;&gt;"",1,N(F255)))</f>
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="32" t="n"/>
@@ -11606,6 +12611,10 @@
         <f>IF(OR(B256="",G256="Concluída"),0,IF(G256="Atrasada",3000+MIN(Config!$B$5-E256,60),IF(G256="Vence em breve",2000-(E256-Config!$B$5),IF(G256="Em andamento",1000-MIN(E256-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L256" s="35">
+        <f>IF(B256="","",IF(I256&lt;&gt;"",1,N(F256)))</f>
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="32" t="n"/>
@@ -11628,6 +12637,10 @@
         <f>IF(OR(B257="",G257="Concluída"),0,IF(G257="Atrasada",3000+MIN(Config!$B$5-E257,60),IF(G257="Vence em breve",2000-(E257-Config!$B$5),IF(G257="Em andamento",1000-MIN(E257-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L257" s="35">
+        <f>IF(B257="","",IF(I257&lt;&gt;"",1,N(F257)))</f>
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="32" t="n"/>
@@ -11650,6 +12663,10 @@
         <f>IF(OR(B258="",G258="Concluída"),0,IF(G258="Atrasada",3000+MIN(Config!$B$5-E258,60),IF(G258="Vence em breve",2000-(E258-Config!$B$5),IF(G258="Em andamento",1000-MIN(E258-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L258" s="35">
+        <f>IF(B258="","",IF(I258&lt;&gt;"",1,N(F258)))</f>
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="32" t="n"/>
@@ -11672,6 +12689,10 @@
         <f>IF(OR(B259="",G259="Concluída"),0,IF(G259="Atrasada",3000+MIN(Config!$B$5-E259,60),IF(G259="Vence em breve",2000-(E259-Config!$B$5),IF(G259="Em andamento",1000-MIN(E259-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L259" s="35">
+        <f>IF(B259="","",IF(I259&lt;&gt;"",1,N(F259)))</f>
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="32" t="n"/>
@@ -11694,6 +12715,10 @@
         <f>IF(OR(B260="",G260="Concluída"),0,IF(G260="Atrasada",3000+MIN(Config!$B$5-E260,60),IF(G260="Vence em breve",2000-(E260-Config!$B$5),IF(G260="Em andamento",1000-MIN(E260-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L260" s="35">
+        <f>IF(B260="","",IF(I260&lt;&gt;"",1,N(F260)))</f>
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="32" t="n"/>
@@ -11716,6 +12741,10 @@
         <f>IF(OR(B261="",G261="Concluída"),0,IF(G261="Atrasada",3000+MIN(Config!$B$5-E261,60),IF(G261="Vence em breve",2000-(E261-Config!$B$5),IF(G261="Em andamento",1000-MIN(E261-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L261" s="35">
+        <f>IF(B261="","",IF(I261&lt;&gt;"",1,N(F261)))</f>
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="32" t="n"/>
@@ -11738,6 +12767,10 @@
         <f>IF(OR(B262="",G262="Concluída"),0,IF(G262="Atrasada",3000+MIN(Config!$B$5-E262,60),IF(G262="Vence em breve",2000-(E262-Config!$B$5),IF(G262="Em andamento",1000-MIN(E262-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L262" s="35">
+        <f>IF(B262="","",IF(I262&lt;&gt;"",1,N(F262)))</f>
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="32" t="n"/>
@@ -11760,6 +12793,10 @@
         <f>IF(OR(B263="",G263="Concluída"),0,IF(G263="Atrasada",3000+MIN(Config!$B$5-E263,60),IF(G263="Vence em breve",2000-(E263-Config!$B$5),IF(G263="Em andamento",1000-MIN(E263-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L263" s="35">
+        <f>IF(B263="","",IF(I263&lt;&gt;"",1,N(F263)))</f>
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="32" t="n"/>
@@ -11782,6 +12819,10 @@
         <f>IF(OR(B264="",G264="Concluída"),0,IF(G264="Atrasada",3000+MIN(Config!$B$5-E264,60),IF(G264="Vence em breve",2000-(E264-Config!$B$5),IF(G264="Em andamento",1000-MIN(E264-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L264" s="35">
+        <f>IF(B264="","",IF(I264&lt;&gt;"",1,N(F264)))</f>
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="32" t="n"/>
@@ -11804,6 +12845,10 @@
         <f>IF(OR(B265="",G265="Concluída"),0,IF(G265="Atrasada",3000+MIN(Config!$B$5-E265,60),IF(G265="Vence em breve",2000-(E265-Config!$B$5),IF(G265="Em andamento",1000-MIN(E265-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L265" s="35">
+        <f>IF(B265="","",IF(I265&lt;&gt;"",1,N(F265)))</f>
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="32" t="n"/>
@@ -11826,6 +12871,10 @@
         <f>IF(OR(B266="",G266="Concluída"),0,IF(G266="Atrasada",3000+MIN(Config!$B$5-E266,60),IF(G266="Vence em breve",2000-(E266-Config!$B$5),IF(G266="Em andamento",1000-MIN(E266-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L266" s="35">
+        <f>IF(B266="","",IF(I266&lt;&gt;"",1,N(F266)))</f>
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="32" t="n"/>
@@ -11848,6 +12897,10 @@
         <f>IF(OR(B267="",G267="Concluída"),0,IF(G267="Atrasada",3000+MIN(Config!$B$5-E267,60),IF(G267="Vence em breve",2000-(E267-Config!$B$5),IF(G267="Em andamento",1000-MIN(E267-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L267" s="35">
+        <f>IF(B267="","",IF(I267&lt;&gt;"",1,N(F267)))</f>
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="32" t="n"/>
@@ -11870,6 +12923,10 @@
         <f>IF(OR(B268="",G268="Concluída"),0,IF(G268="Atrasada",3000+MIN(Config!$B$5-E268,60),IF(G268="Vence em breve",2000-(E268-Config!$B$5),IF(G268="Em andamento",1000-MIN(E268-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L268" s="35">
+        <f>IF(B268="","",IF(I268&lt;&gt;"",1,N(F268)))</f>
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="32" t="n"/>
@@ -11892,6 +12949,10 @@
         <f>IF(OR(B269="",G269="Concluída"),0,IF(G269="Atrasada",3000+MIN(Config!$B$5-E269,60),IF(G269="Vence em breve",2000-(E269-Config!$B$5),IF(G269="Em andamento",1000-MIN(E269-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L269" s="35">
+        <f>IF(B269="","",IF(I269&lt;&gt;"",1,N(F269)))</f>
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="32" t="n"/>
@@ -11914,6 +12975,10 @@
         <f>IF(OR(B270="",G270="Concluída"),0,IF(G270="Atrasada",3000+MIN(Config!$B$5-E270,60),IF(G270="Vence em breve",2000-(E270-Config!$B$5),IF(G270="Em andamento",1000-MIN(E270-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L270" s="35">
+        <f>IF(B270="","",IF(I270&lt;&gt;"",1,N(F270)))</f>
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="32" t="n"/>
@@ -11936,6 +13001,10 @@
         <f>IF(OR(B271="",G271="Concluída"),0,IF(G271="Atrasada",3000+MIN(Config!$B$5-E271,60),IF(G271="Vence em breve",2000-(E271-Config!$B$5),IF(G271="Em andamento",1000-MIN(E271-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L271" s="35">
+        <f>IF(B271="","",IF(I271&lt;&gt;"",1,N(F271)))</f>
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="32" t="n"/>
@@ -11958,6 +13027,10 @@
         <f>IF(OR(B272="",G272="Concluída"),0,IF(G272="Atrasada",3000+MIN(Config!$B$5-E272,60),IF(G272="Vence em breve",2000-(E272-Config!$B$5),IF(G272="Em andamento",1000-MIN(E272-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L272" s="35">
+        <f>IF(B272="","",IF(I272&lt;&gt;"",1,N(F272)))</f>
+        <v/>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="32" t="n"/>
@@ -11980,6 +13053,10 @@
         <f>IF(OR(B273="",G273="Concluída"),0,IF(G273="Atrasada",3000+MIN(Config!$B$5-E273,60),IF(G273="Vence em breve",2000-(E273-Config!$B$5),IF(G273="Em andamento",1000-MIN(E273-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L273" s="35">
+        <f>IF(B273="","",IF(I273&lt;&gt;"",1,N(F273)))</f>
+        <v/>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="32" t="n"/>
@@ -12002,6 +13079,10 @@
         <f>IF(OR(B274="",G274="Concluída"),0,IF(G274="Atrasada",3000+MIN(Config!$B$5-E274,60),IF(G274="Vence em breve",2000-(E274-Config!$B$5),IF(G274="Em andamento",1000-MIN(E274-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L274" s="35">
+        <f>IF(B274="","",IF(I274&lt;&gt;"",1,N(F274)))</f>
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="32" t="n"/>
@@ -12024,6 +13105,10 @@
         <f>IF(OR(B275="",G275="Concluída"),0,IF(G275="Atrasada",3000+MIN(Config!$B$5-E275,60),IF(G275="Vence em breve",2000-(E275-Config!$B$5),IF(G275="Em andamento",1000-MIN(E275-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L275" s="35">
+        <f>IF(B275="","",IF(I275&lt;&gt;"",1,N(F275)))</f>
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="32" t="n"/>
@@ -12046,6 +13131,10 @@
         <f>IF(OR(B276="",G276="Concluída"),0,IF(G276="Atrasada",3000+MIN(Config!$B$5-E276,60),IF(G276="Vence em breve",2000-(E276-Config!$B$5),IF(G276="Em andamento",1000-MIN(E276-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L276" s="35">
+        <f>IF(B276="","",IF(I276&lt;&gt;"",1,N(F276)))</f>
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="32" t="n"/>
@@ -12068,6 +13157,10 @@
         <f>IF(OR(B277="",G277="Concluída"),0,IF(G277="Atrasada",3000+MIN(Config!$B$5-E277,60),IF(G277="Vence em breve",2000-(E277-Config!$B$5),IF(G277="Em andamento",1000-MIN(E277-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L277" s="35">
+        <f>IF(B277="","",IF(I277&lt;&gt;"",1,N(F277)))</f>
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="32" t="n"/>
@@ -12090,6 +13183,10 @@
         <f>IF(OR(B278="",G278="Concluída"),0,IF(G278="Atrasada",3000+MIN(Config!$B$5-E278,60),IF(G278="Vence em breve",2000-(E278-Config!$B$5),IF(G278="Em andamento",1000-MIN(E278-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L278" s="35">
+        <f>IF(B278="","",IF(I278&lt;&gt;"",1,N(F278)))</f>
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="32" t="n"/>
@@ -12112,6 +13209,10 @@
         <f>IF(OR(B279="",G279="Concluída"),0,IF(G279="Atrasada",3000+MIN(Config!$B$5-E279,60),IF(G279="Vence em breve",2000-(E279-Config!$B$5),IF(G279="Em andamento",1000-MIN(E279-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L279" s="35">
+        <f>IF(B279="","",IF(I279&lt;&gt;"",1,N(F279)))</f>
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="32" t="n"/>
@@ -12134,6 +13235,10 @@
         <f>IF(OR(B280="",G280="Concluída"),0,IF(G280="Atrasada",3000+MIN(Config!$B$5-E280,60),IF(G280="Vence em breve",2000-(E280-Config!$B$5),IF(G280="Em andamento",1000-MIN(E280-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L280" s="35">
+        <f>IF(B280="","",IF(I280&lt;&gt;"",1,N(F280)))</f>
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="32" t="n"/>
@@ -12156,6 +13261,10 @@
         <f>IF(OR(B281="",G281="Concluída"),0,IF(G281="Atrasada",3000+MIN(Config!$B$5-E281,60),IF(G281="Vence em breve",2000-(E281-Config!$B$5),IF(G281="Em andamento",1000-MIN(E281-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L281" s="35">
+        <f>IF(B281="","",IF(I281&lt;&gt;"",1,N(F281)))</f>
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="32" t="n"/>
@@ -12178,6 +13287,10 @@
         <f>IF(OR(B282="",G282="Concluída"),0,IF(G282="Atrasada",3000+MIN(Config!$B$5-E282,60),IF(G282="Vence em breve",2000-(E282-Config!$B$5),IF(G282="Em andamento",1000-MIN(E282-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L282" s="35">
+        <f>IF(B282="","",IF(I282&lt;&gt;"",1,N(F282)))</f>
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="32" t="n"/>
@@ -12200,6 +13313,10 @@
         <f>IF(OR(B283="",G283="Concluída"),0,IF(G283="Atrasada",3000+MIN(Config!$B$5-E283,60),IF(G283="Vence em breve",2000-(E283-Config!$B$5),IF(G283="Em andamento",1000-MIN(E283-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L283" s="35">
+        <f>IF(B283="","",IF(I283&lt;&gt;"",1,N(F283)))</f>
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="32" t="n"/>
@@ -12222,6 +13339,10 @@
         <f>IF(OR(B284="",G284="Concluída"),0,IF(G284="Atrasada",3000+MIN(Config!$B$5-E284,60),IF(G284="Vence em breve",2000-(E284-Config!$B$5),IF(G284="Em andamento",1000-MIN(E284-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L284" s="35">
+        <f>IF(B284="","",IF(I284&lt;&gt;"",1,N(F284)))</f>
+        <v/>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="32" t="n"/>
@@ -12244,6 +13365,10 @@
         <f>IF(OR(B285="",G285="Concluída"),0,IF(G285="Atrasada",3000+MIN(Config!$B$5-E285,60),IF(G285="Vence em breve",2000-(E285-Config!$B$5),IF(G285="Em andamento",1000-MIN(E285-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L285" s="35">
+        <f>IF(B285="","",IF(I285&lt;&gt;"",1,N(F285)))</f>
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="32" t="n"/>
@@ -12266,6 +13391,10 @@
         <f>IF(OR(B286="",G286="Concluída"),0,IF(G286="Atrasada",3000+MIN(Config!$B$5-E286,60),IF(G286="Vence em breve",2000-(E286-Config!$B$5),IF(G286="Em andamento",1000-MIN(E286-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L286" s="35">
+        <f>IF(B286="","",IF(I286&lt;&gt;"",1,N(F286)))</f>
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="32" t="n"/>
@@ -12288,6 +13417,10 @@
         <f>IF(OR(B287="",G287="Concluída"),0,IF(G287="Atrasada",3000+MIN(Config!$B$5-E287,60),IF(G287="Vence em breve",2000-(E287-Config!$B$5),IF(G287="Em andamento",1000-MIN(E287-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L287" s="35">
+        <f>IF(B287="","",IF(I287&lt;&gt;"",1,N(F287)))</f>
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="32" t="n"/>
@@ -12310,6 +13443,10 @@
         <f>IF(OR(B288="",G288="Concluída"),0,IF(G288="Atrasada",3000+MIN(Config!$B$5-E288,60),IF(G288="Vence em breve",2000-(E288-Config!$B$5),IF(G288="Em andamento",1000-MIN(E288-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L288" s="35">
+        <f>IF(B288="","",IF(I288&lt;&gt;"",1,N(F288)))</f>
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="32" t="n"/>
@@ -12332,6 +13469,10 @@
         <f>IF(OR(B289="",G289="Concluída"),0,IF(G289="Atrasada",3000+MIN(Config!$B$5-E289,60),IF(G289="Vence em breve",2000-(E289-Config!$B$5),IF(G289="Em andamento",1000-MIN(E289-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L289" s="35">
+        <f>IF(B289="","",IF(I289&lt;&gt;"",1,N(F289)))</f>
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="32" t="n"/>
@@ -12354,6 +13495,10 @@
         <f>IF(OR(B290="",G290="Concluída"),0,IF(G290="Atrasada",3000+MIN(Config!$B$5-E290,60),IF(G290="Vence em breve",2000-(E290-Config!$B$5),IF(G290="Em andamento",1000-MIN(E290-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L290" s="35">
+        <f>IF(B290="","",IF(I290&lt;&gt;"",1,N(F290)))</f>
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="32" t="n"/>
@@ -12376,6 +13521,10 @@
         <f>IF(OR(B291="",G291="Concluída"),0,IF(G291="Atrasada",3000+MIN(Config!$B$5-E291,60),IF(G291="Vence em breve",2000-(E291-Config!$B$5),IF(G291="Em andamento",1000-MIN(E291-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L291" s="35">
+        <f>IF(B291="","",IF(I291&lt;&gt;"",1,N(F291)))</f>
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="32" t="n"/>
@@ -12398,6 +13547,10 @@
         <f>IF(OR(B292="",G292="Concluída"),0,IF(G292="Atrasada",3000+MIN(Config!$B$5-E292,60),IF(G292="Vence em breve",2000-(E292-Config!$B$5),IF(G292="Em andamento",1000-MIN(E292-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L292" s="35">
+        <f>IF(B292="","",IF(I292&lt;&gt;"",1,N(F292)))</f>
+        <v/>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="32" t="n"/>
@@ -12420,6 +13573,10 @@
         <f>IF(OR(B293="",G293="Concluída"),0,IF(G293="Atrasada",3000+MIN(Config!$B$5-E293,60),IF(G293="Vence em breve",2000-(E293-Config!$B$5),IF(G293="Em andamento",1000-MIN(E293-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L293" s="35">
+        <f>IF(B293="","",IF(I293&lt;&gt;"",1,N(F293)))</f>
+        <v/>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="32" t="n"/>
@@ -12442,6 +13599,10 @@
         <f>IF(OR(B294="",G294="Concluída"),0,IF(G294="Atrasada",3000+MIN(Config!$B$5-E294,60),IF(G294="Vence em breve",2000-(E294-Config!$B$5),IF(G294="Em andamento",1000-MIN(E294-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L294" s="35">
+        <f>IF(B294="","",IF(I294&lt;&gt;"",1,N(F294)))</f>
+        <v/>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="32" t="n"/>
@@ -12464,6 +13625,10 @@
         <f>IF(OR(B295="",G295="Concluída"),0,IF(G295="Atrasada",3000+MIN(Config!$B$5-E295,60),IF(G295="Vence em breve",2000-(E295-Config!$B$5),IF(G295="Em andamento",1000-MIN(E295-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L295" s="35">
+        <f>IF(B295="","",IF(I295&lt;&gt;"",1,N(F295)))</f>
+        <v/>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="32" t="n"/>
@@ -12486,6 +13651,10 @@
         <f>IF(OR(B296="",G296="Concluída"),0,IF(G296="Atrasada",3000+MIN(Config!$B$5-E296,60),IF(G296="Vence em breve",2000-(E296-Config!$B$5),IF(G296="Em andamento",1000-MIN(E296-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L296" s="35">
+        <f>IF(B296="","",IF(I296&lt;&gt;"",1,N(F296)))</f>
+        <v/>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="32" t="n"/>
@@ -12508,6 +13677,10 @@
         <f>IF(OR(B297="",G297="Concluída"),0,IF(G297="Atrasada",3000+MIN(Config!$B$5-E297,60),IF(G297="Vence em breve",2000-(E297-Config!$B$5),IF(G297="Em andamento",1000-MIN(E297-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L297" s="35">
+        <f>IF(B297="","",IF(I297&lt;&gt;"",1,N(F297)))</f>
+        <v/>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="32" t="n"/>
@@ -12530,6 +13703,10 @@
         <f>IF(OR(B298="",G298="Concluída"),0,IF(G298="Atrasada",3000+MIN(Config!$B$5-E298,60),IF(G298="Vence em breve",2000-(E298-Config!$B$5),IF(G298="Em andamento",1000-MIN(E298-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L298" s="35">
+        <f>IF(B298="","",IF(I298&lt;&gt;"",1,N(F298)))</f>
+        <v/>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="32" t="n"/>
@@ -12552,6 +13729,10 @@
         <f>IF(OR(B299="",G299="Concluída"),0,IF(G299="Atrasada",3000+MIN(Config!$B$5-E299,60),IF(G299="Vence em breve",2000-(E299-Config!$B$5),IF(G299="Em andamento",1000-MIN(E299-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L299" s="35">
+        <f>IF(B299="","",IF(I299&lt;&gt;"",1,N(F299)))</f>
+        <v/>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="32" t="n"/>
@@ -12574,6 +13755,10 @@
         <f>IF(OR(B300="",G300="Concluída"),0,IF(G300="Atrasada",3000+MIN(Config!$B$5-E300,60),IF(G300="Vence em breve",2000-(E300-Config!$B$5),IF(G300="Em andamento",1000-MIN(E300-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L300" s="35">
+        <f>IF(B300="","",IF(I300&lt;&gt;"",1,N(F300)))</f>
+        <v/>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="32" t="n"/>
@@ -12596,6 +13781,10 @@
         <f>IF(OR(B301="",G301="Concluída"),0,IF(G301="Atrasada",3000+MIN(Config!$B$5-E301,60),IF(G301="Vence em breve",2000-(E301-Config!$B$5),IF(G301="Em andamento",1000-MIN(E301-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L301" s="35">
+        <f>IF(B301="","",IF(I301&lt;&gt;"",1,N(F301)))</f>
+        <v/>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="32" t="n"/>
@@ -12618,6 +13807,10 @@
         <f>IF(OR(B302="",G302="Concluída"),0,IF(G302="Atrasada",3000+MIN(Config!$B$5-E302,60),IF(G302="Vence em breve",2000-(E302-Config!$B$5),IF(G302="Em andamento",1000-MIN(E302-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L302" s="35">
+        <f>IF(B302="","",IF(I302&lt;&gt;"",1,N(F302)))</f>
+        <v/>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="32" t="n"/>
@@ -12640,6 +13833,10 @@
         <f>IF(OR(B303="",G303="Concluída"),0,IF(G303="Atrasada",3000+MIN(Config!$B$5-E303,60),IF(G303="Vence em breve",2000-(E303-Config!$B$5),IF(G303="Em andamento",1000-MIN(E303-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
       </c>
+      <c r="L303" s="35">
+        <f>IF(B303="","",IF(I303&lt;&gt;"",1,N(F303)))</f>
+        <v/>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="32" t="n"/>
@@ -12661,6 +13858,10 @@
       <c r="K304" s="35">
         <f>IF(OR(B304="",G304="Concluída"),0,IF(G304="Atrasada",3000+MIN(Config!$B$5-E304,60),IF(G304="Vence em breve",2000-(E304-Config!$B$5),IF(G304="Em andamento",1000-MIN(E304-Config!$B$5,900),100)))-ROW()/100000)</f>
         <v>0</v>
+      </c>
+      <c r="L304" s="35">
+        <f>IF(B304="","",IF(I304&lt;&gt;"",1,N(F304)))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -12681,16 +13882,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="A5:A304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Config!$A$10:$A$19</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Config!$A$22:$A$31</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:E304 I5:I304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="D5:E304 I5:I304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Digite entre 0% e 100%" type="decimal" operator="between">
+    <dataValidation sqref="F5:F304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Digite entre 0% e 100%" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/04-projetos-e-prazos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/04-projetos-e-prazos.xlsx
@@ -22,9 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="dd/mm"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="dd/mm"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -267,7 +268,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -277,7 +278,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -287,14 +288,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -753,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -794,7 +795,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Em Config, preencha o nome da equipe, deixe a data de referência em =HOJE(), cadastre até 10 projetos (nome, cliente, responsável, início e prazo final) e as pessoas da equipe.</t>
+          <t>Em Config, preencha o nome da equipe, troque a data de referência por =HOJE() (no exemplo ela está congelada em 14/09/2026), cadastre até 10 projetos (nome, cliente, responsável, início e prazo final) e as pessoas da equipe.</t>
         </is>
       </c>
     </row>
@@ -873,34 +874,58 @@
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Google Sheets</t>
+          <t>Requisitos</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Exemplos</t>
+          <t>Google Sheets</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Prisma Comunicação é uma empresa fictícia. Nomes e valores são inventados. Apague-os antes de começar.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Exemplos</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Prisma Comunicação é uma empresa fictícia. Nomes e valores são inventados. Apague-os antes de começar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -934,7 +959,7 @@
     <row r="1">
       <c r="A1" s="5" t="str">
         <f>Config!B4&amp;" · painel de "&amp;TEXT(Config!B5,"dd/mm/yyyy")</f>
-        <v>Prisma Comunicação (exemplo fictício) · painel de 17/09/2026</v>
+        <v>Prisma Comunicação (exemplo fictício) · painel de 14/09/2026</v>
       </c>
     </row>
     <row r="2">
@@ -1463,7 +1488,7 @@
       </c>
       <c r="G23" s="25">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,1)&gt;0,INDEX(Etapas!$H$5:$H$304,MATCH(LARGE(Etapas!$K$5:$K$304,1),Etapas!$K$5:$K$304,0)),""),"")</f>
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="H23" s="24">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,1)&gt;0,INDEX(Etapas!$F$5:$F$304,MATCH(LARGE(Etapas!$K$5:$K$304,1),Etapas!$K$5:$K$304,0)),""),"")</f>
@@ -1496,7 +1521,7 @@
       </c>
       <c r="G24" s="25">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,2)&gt;0,INDEX(Etapas!$H$5:$H$304,MATCH(LARGE(Etapas!$K$5:$K$304,2),Etapas!$K$5:$K$304,0)),""),"")</f>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="H24" s="24">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,2)&gt;0,INDEX(Etapas!$F$5:$F$304,MATCH(LARGE(Etapas!$K$5:$K$304,2),Etapas!$K$5:$K$304,0)),""),"")</f>
@@ -1529,7 +1554,7 @@
       </c>
       <c r="G25" s="25">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,3)&gt;0,INDEX(Etapas!$H$5:$H$304,MATCH(LARGE(Etapas!$K$5:$K$304,3),Etapas!$K$5:$K$304,0)),""),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25" s="24">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,3)&gt;0,INDEX(Etapas!$F$5:$F$304,MATCH(LARGE(Etapas!$K$5:$K$304,3),Etapas!$K$5:$K$304,0)),""),"")</f>
@@ -1562,7 +1587,7 @@
       </c>
       <c r="G26" s="25">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,4)&gt;0,INDEX(Etapas!$H$5:$H$304,MATCH(LARGE(Etapas!$K$5:$K$304,4),Etapas!$K$5:$K$304,0)),""),"")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H26" s="24">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,4)&gt;0,INDEX(Etapas!$F$5:$F$304,MATCH(LARGE(Etapas!$K$5:$K$304,4),Etapas!$K$5:$K$304,0)),""),"")</f>
@@ -1595,7 +1620,7 @@
       </c>
       <c r="G27" s="25">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,5)&gt;0,INDEX(Etapas!$H$5:$H$304,MATCH(LARGE(Etapas!$K$5:$K$304,5),Etapas!$K$5:$K$304,0)),""),"")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H27" s="24">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,5)&gt;0,INDEX(Etapas!$F$5:$F$304,MATCH(LARGE(Etapas!$K$5:$K$304,5),Etapas!$K$5:$K$304,0)),""),"")</f>
@@ -1628,7 +1653,7 @@
       </c>
       <c r="G28" s="25">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,6)&gt;0,INDEX(Etapas!$H$5:$H$304,MATCH(LARGE(Etapas!$K$5:$K$304,6),Etapas!$K$5:$K$304,0)),""),"")</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H28" s="24">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,6)&gt;0,INDEX(Etapas!$F$5:$F$304,MATCH(LARGE(Etapas!$K$5:$K$304,6),Etapas!$K$5:$K$304,0)),""),"")</f>
@@ -1661,7 +1686,7 @@
       </c>
       <c r="G29" s="25">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,7)&gt;0,INDEX(Etapas!$H$5:$H$304,MATCH(LARGE(Etapas!$K$5:$K$304,7),Etapas!$K$5:$K$304,0)),""),"")</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H29" s="24">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,7)&gt;0,INDEX(Etapas!$F$5:$F$304,MATCH(LARGE(Etapas!$K$5:$K$304,7),Etapas!$K$5:$K$304,0)),""),"")</f>
@@ -1694,7 +1719,7 @@
       </c>
       <c r="G30" s="25">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,8)&gt;0,INDEX(Etapas!$H$5:$H$304,MATCH(LARGE(Etapas!$K$5:$K$304,8),Etapas!$K$5:$K$304,0)),""),"")</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H30" s="24">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,8)&gt;0,INDEX(Etapas!$F$5:$F$304,MATCH(LARGE(Etapas!$K$5:$K$304,8),Etapas!$K$5:$K$304,0)),""),"")</f>
@@ -1727,7 +1752,7 @@
       </c>
       <c r="G31" s="25">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,9)&gt;0,INDEX(Etapas!$H$5:$H$304,MATCH(LARGE(Etapas!$K$5:$K$304,9),Etapas!$K$5:$K$304,0)),""),"")</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H31" s="24">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,9)&gt;0,INDEX(Etapas!$F$5:$F$304,MATCH(LARGE(Etapas!$K$5:$K$304,9),Etapas!$K$5:$K$304,0)),""),"")</f>
@@ -1760,7 +1785,7 @@
       </c>
       <c r="G32" s="25">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,10)&gt;0,INDEX(Etapas!$H$5:$H$304,MATCH(LARGE(Etapas!$K$5:$K$304,10),Etapas!$K$5:$K$304,0)),""),"")</f>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H32" s="24">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,10)&gt;0,INDEX(Etapas!$F$5:$F$304,MATCH(LARGE(Etapas!$K$5:$K$304,10),Etapas!$K$5:$K$304,0)),""),"")</f>
@@ -1793,7 +1818,7 @@
       </c>
       <c r="G33" s="25">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,11)&gt;0,INDEX(Etapas!$H$5:$H$304,MATCH(LARGE(Etapas!$K$5:$K$304,11),Etapas!$K$5:$K$304,0)),""),"")</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H33" s="24">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,11)&gt;0,INDEX(Etapas!$F$5:$F$304,MATCH(LARGE(Etapas!$K$5:$K$304,11),Etapas!$K$5:$K$304,0)),""),"")</f>
@@ -1826,7 +1851,7 @@
       </c>
       <c r="G34" s="25">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,12)&gt;0,INDEX(Etapas!$H$5:$H$304,MATCH(LARGE(Etapas!$K$5:$K$304,12),Etapas!$K$5:$K$304,0)),""),"")</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H34" s="24">
         <f>IFERROR(IF(LARGE(Etapas!$K$5:$K$304,12)&gt;0,INDEX(Etapas!$F$5:$F$304,MATCH(LARGE(Etapas!$K$5:$K$304,12),Etapas!$K$5:$K$304,0)),""),"")</f>
@@ -5299,13 +5324,12 @@
           <t>Data de referência (hoje)</t>
         </is>
       </c>
-      <c r="B5" s="31">
-        <f>TODAY()</f>
-        <v>46282.0</v>
+      <c r="B5" s="31" t="n">
+        <v>46279</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Deixe =HOJE() para acompanhar o dia; troque por uma data para simular.</t>
+          <t>O exemplo está congelado em 14/09/2026, para os arquivos do kit mostrarem a mesma foto. Ao usar com os seus dados, troque por =HOJE().</t>
         </is>
       </c>
     </row>
@@ -5857,13 +5881,13 @@
       </c>
       <c r="H8" s="25">
         <f>IF(OR(B8="",G8="Concluída"),"",E8-Config!$B$5)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I8" s="33" t="n"/>
       <c r="J8" s="30" t="n"/>
       <c r="K8" s="35">
         <f>IF(OR(B8="",G8="Concluída"),0,IF(G8="Atrasada",3000+MIN(Config!$B$5-E8,60),IF(G8="Vence em breve",2000-(E8-Config!$B$5),IF(G8="Em andamento",1000-MIN(E8-Config!$B$5,900),100)))-ROW()/100000)</f>
-        <v>1997.99992</v>
+        <v>1994.99992</v>
       </c>
       <c r="L8" s="35">
         <f>IF(B8="","",IF(I8&lt;&gt;"",1,N(F8)))</f>
@@ -5901,13 +5925,13 @@
       </c>
       <c r="H9" s="25">
         <f>IF(OR(B9="",G9="Concluída"),"",E9-Config!$B$5)</f>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="I9" s="33" t="n"/>
       <c r="J9" s="30" t="n"/>
       <c r="K9" s="35">
         <f>IF(OR(B9="",G9="Concluída"),0,IF(G9="Atrasada",3000+MIN(Config!$B$5-E9,60),IF(G9="Vence em breve",2000-(E9-Config!$B$5),IF(G9="Em andamento",1000-MIN(E9-Config!$B$5,900),100)))-ROW()/100000)</f>
-        <v>3004.99991</v>
+        <v>3001.99991</v>
       </c>
       <c r="L9" s="35">
         <f>IF(B9="","",IF(I9&lt;&gt;"",1,N(F9)))</f>
@@ -5945,7 +5969,7 @@
       </c>
       <c r="H10" s="25">
         <f>IF(OR(B10="",G10="Concluída"),"",E10-Config!$B$5)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I10" s="33" t="n"/>
       <c r="J10" s="30" t="n"/>
@@ -5989,7 +6013,7 @@
       </c>
       <c r="H11" s="25">
         <f>IF(OR(B11="",G11="Concluída"),"",E11-Config!$B$5)</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I11" s="33" t="n"/>
       <c r="J11" s="30" t="n"/>
@@ -6079,13 +6103,13 @@
       </c>
       <c r="H13" s="25">
         <f>IF(OR(B13="",G13="Concluída"),"",E13-Config!$B$5)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" s="33" t="n"/>
       <c r="J13" s="30" t="n"/>
       <c r="K13" s="35">
         <f>IF(OR(B13="",G13="Concluída"),0,IF(G13="Atrasada",3000+MIN(Config!$B$5-E13,60),IF(G13="Vence em breve",2000-(E13-Config!$B$5),IF(G13="Em andamento",1000-MIN(E13-Config!$B$5,900),100)))-ROW()/100000)</f>
-        <v>1999.99987</v>
+        <v>1996.99987</v>
       </c>
       <c r="L13" s="35">
         <f>IF(B13="","",IF(I13&lt;&gt;"",1,N(F13)))</f>
@@ -6123,7 +6147,7 @@
       </c>
       <c r="H14" s="25">
         <f>IF(OR(B14="",G14="Concluída"),"",E14-Config!$B$5)</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I14" s="33" t="n"/>
       <c r="J14" s="30" t="n"/>
@@ -6167,7 +6191,7 @@
       </c>
       <c r="H15" s="25">
         <f>IF(OR(B15="",G15="Concluída"),"",E15-Config!$B$5)</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I15" s="33" t="n"/>
       <c r="J15" s="30" t="n"/>
@@ -6211,7 +6235,7 @@
       </c>
       <c r="H16" s="25">
         <f>IF(OR(B16="",G16="Concluída"),"",E16-Config!$B$5)</f>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I16" s="33" t="n"/>
       <c r="J16" s="30" t="n"/>
@@ -6301,13 +6325,13 @@
       </c>
       <c r="H18" s="25">
         <f>IF(OR(B18="",G18="Concluída"),"",E18-Config!$B$5)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I18" s="33" t="n"/>
       <c r="J18" s="30" t="n"/>
       <c r="K18" s="35">
         <f>IF(OR(B18="",G18="Concluída"),0,IF(G18="Atrasada",3000+MIN(Config!$B$5-E18,60),IF(G18="Vence em breve",2000-(E18-Config!$B$5),IF(G18="Em andamento",1000-MIN(E18-Config!$B$5,900),100)))-ROW()/100000)</f>
-        <v>1997.99982</v>
+        <v>1994.99982</v>
       </c>
       <c r="L18" s="35">
         <f>IF(B18="","",IF(I18&lt;&gt;"",1,N(F18)))</f>
@@ -6345,7 +6369,7 @@
       </c>
       <c r="H19" s="25">
         <f>IF(OR(B19="",G19="Concluída"),"",E19-Config!$B$5)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I19" s="33" t="n"/>
       <c r="J19" s="30" t="n"/>
@@ -6389,7 +6413,7 @@
       </c>
       <c r="H20" s="25">
         <f>IF(OR(B20="",G20="Concluída"),"",E20-Config!$B$5)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I20" s="33" t="n"/>
       <c r="J20" s="30" t="n"/>
@@ -6571,13 +6595,13 @@
       </c>
       <c r="H24" s="25">
         <f>IF(OR(B24="",G24="Concluída"),"",E24-Config!$B$5)</f>
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="I24" s="33" t="n"/>
       <c r="J24" s="30" t="n"/>
       <c r="K24" s="35">
         <f>IF(OR(B24="",G24="Concluída"),0,IF(G24="Atrasada",3000+MIN(Config!$B$5-E24,60),IF(G24="Vence em breve",2000-(E24-Config!$B$5),IF(G24="Em andamento",1000-MIN(E24-Config!$B$5,900),100)))-ROW()/100000)</f>
-        <v>3011.99976</v>
+        <v>3008.99976</v>
       </c>
       <c r="L24" s="35">
         <f>IF(B24="","",IF(I24&lt;&gt;"",1,N(F24)))</f>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/04-projetos-e-prazos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/04-projetos-e-prazos.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:R4">
     <cfRule type="expression" priority="4" dxfId="7">
-      <formula>AND(E$4&lt;=Config!$B$5,E$4+6&gt;=Config!$B$5)</formula>
+      <formula>AND(E$4&lt;=INDIRECT("Config!$B$5"),E$4+6&gt;=INDIRECT("Config!$B$5"))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/04-projetos-e-prazos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/04-projetos-e-prazos.xlsx
@@ -796,6 +796,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -912,7 +913,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e semáforos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
